--- a/pricing/tarife.xlsx
+++ b/pricing/tarife.xlsx
@@ -1,125 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mirce\Documents\Silver Mountain\AI site Travel Concept\pricing\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8865B53C-4557-432B-9AD7-CFD4D58EE1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="2880" windowWidth="14595" windowHeight="7800" xr2:uid="{8C837C14-878E-4F00-B236-80FFA3F6097F}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2850" yWindow="2880" windowWidth="14595" windowHeight="7800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Foaie1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foaie1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
-  <si>
-    <t>Data inceput</t>
-  </si>
-  <si>
-    <t>Data sfarsit</t>
-  </si>
-  <si>
-    <t>pret referinta</t>
-  </si>
-  <si>
-    <t>iarna-2026</t>
-  </si>
-  <si>
-    <t>2 zile</t>
-  </si>
-  <si>
-    <t>3 zile</t>
-  </si>
-  <si>
-    <t>4 zile</t>
-  </si>
-  <si>
-    <t>5 zile</t>
-  </si>
-  <si>
-    <t>6 zile</t>
-  </si>
-  <si>
-    <t>7 zile</t>
-  </si>
-  <si>
-    <t>vara-toamna-2026</t>
-  </si>
-  <si>
-    <t>Craciun-2026</t>
-  </si>
-  <si>
-    <t>Revelion-2026-2027</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>label</t>
-  </si>
-  <si>
-    <t>Sezon vară</t>
-  </si>
-  <si>
-    <t>Sezon iarnă</t>
-  </si>
-  <si>
-    <t>Vacanta-schi-2027</t>
-  </si>
-  <si>
-    <t>iarna-2027</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-418]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -143,46 +61,108 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -482,256 +462,290 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A8B1FF-EB28-4AFD-A90C-3F8A3117C26E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B3:L9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="8.85546875" style="1"/>
+    <col width="18.28515625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="18.28515625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
+    <col width="11.85546875" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="8.85546875" customWidth="1" style="1" min="7" max="12"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Data inceput</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Data sfarsit</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>pret referinta</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>2 zile</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>3 zile</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>4 zile</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>5 zile</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>6 zile</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>7 zile</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>vara-toamna-2026</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Sezon vară</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>iarna-2026</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sezon iarnă</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>46357</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46376</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Craciun-2026</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Sezon iarnă</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>46377</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46383</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46204</v>
-      </c>
-      <c r="E4" s="2">
-        <v>46356</v>
-      </c>
-      <c r="F4" s="8">
-        <v>900</v>
-      </c>
-      <c r="G4" s="5">
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Revelion-2026-2027</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Sezon iarnă</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>46384</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46391</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>iarna-2027</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Sezon iarnă</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>46392</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46432</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H8" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I8" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J8" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K8" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L8" s="5" t="n">
         <v>0.33</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46357</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46376</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1000</v>
-      </c>
-      <c r="G5" s="5">
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Vacanta-schi-2027</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Sezon iarnă</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>46433</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46453</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H9" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I9" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J9" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K9" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="L5" s="5">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46377</v>
-      </c>
-      <c r="E6" s="2">
-        <v>46383</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1200</v>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46384</v>
-      </c>
-      <c r="E7" s="2">
-        <v>46391</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1500</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46392</v>
-      </c>
-      <c r="E8" s="2">
-        <v>46432</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46433</v>
-      </c>
-      <c r="E9" s="2">
-        <v>46453</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1200</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="L9" s="5">
+      <c r="L9" s="5" t="n">
         <v>0.33</v>
       </c>
     </row>

--- a/pricing/tarife.xlsx
+++ b/pricing/tarife.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="260">
   <si>
     <t xml:space="preserve">Strategia de prețuri – Travel Concept - Silver Mountain (A13)</t>
   </si>
@@ -817,7 +817,7 @@
     <t xml:space="preserve">Ultima zi cu tarif pe site</t>
   </si>
   <si>
-    <t xml:space="preserve">Date actuale – citite din conturi pe 21.10.2026</t>
+    <t xml:space="preserve">Date actuale – setate și verificate live în conturi pe 21.10.2026, ora 17:30</t>
   </si>
   <si>
     <t xml:space="preserve">Instantaneu pentru comparație. Actualizează-l când verifici din nou platformele.</t>
@@ -838,15 +838,18 @@
     <t xml:space="preserve">Note</t>
   </si>
   <si>
-    <t xml:space="preserve">21.10 – 30.11.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airbnb/Travelminit cu 64% peste site/Booking</t>
+    <t xml:space="preserve">22.10 – 30.11.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setat 21.10.2026 conform tabelului (înainte: Booking 900, Airbnb 1.480, Travelminit 1.480). Site 900. Ocupat: 28.10–03.11, 28–29.11.</t>
   </si>
   <si>
     <t xml:space="preserve">01.12 – 20.12.2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Setat 21.10.2026 conform tabelului (înainte 1.300 peste tot). Site 1.250.</t>
+  </si>
+  <si>
     <t xml:space="preserve">21.12 – 27.12.2026</t>
   </si>
   <si>
@@ -883,7 +886,7 @@
     <t xml:space="preserve">Booking: Standard Rate nerambursabil; planuri derivate 2–7 zile (-10% … -33%), flexibile 14 zile; plan „Sarbatori – Nerambursabil”; Mobile rate 10% activ din 07.06.2026; Genius neactiv.</t>
   </si>
   <si>
-    <t xml:space="preserve">Airbnb: preț de bază 1.480 lei → câștigi 1.251 lei (taxă unică gazdă ≈15,5%); reducere săptămânală 32%, lunară 33%; sejur 2–30 nopți; tarifare inteligentă oprită; sugestia Airbnb: 531 lei.</t>
+    <t xml:space="preserve">Airbnb: (verificat la 1.480 lei → câștigi 1.251 lei (taxă unică gazdă ≈15,5%)); reducerile 2–6 nopți șterse, rămân săptămânală 32%, lunară 33%; sejur 2–30 nopți; tarifare inteligentă oprită; sugestia Airbnb: 531 lei.</t>
   </si>
   <si>
     <t xml:space="preserve">Travelminit: nivel de comision net 12%; poziția 41 în Poiana Brașov (apartamente); reducere pe mobil afișată ca activă; nopți minime nesetate (Automatic); politică „sarbatori” cu avans.</t>
@@ -1864,41 +1867,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5157,15 +5160,15 @@
       </c>
       <c r="L5" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$6="","",IFERROR(INDEX('Date actuale'!$C$6:$C$40,MATCH(A5,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>900</v>
+        <v>1130</v>
       </c>
       <c r="M5" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$6="","",IFERROR(INDEX('Date actuale'!$D$6:$D$40,MATCH(A5,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1480</v>
+        <v>920</v>
       </c>
       <c r="N5" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$6="","",IFERROR(INDEX('Date actuale'!$E$6:$E$40,MATCH(A5,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1480</v>
+        <v>980</v>
       </c>
       <c r="O5" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$6="","",Sezoane!M6)</f>
@@ -5243,15 +5246,15 @@
       </c>
       <c r="L6" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$7="","",IFERROR(INDEX('Date actuale'!$C$6:$C$40,MATCH(A6,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1300</v>
+        <v>1580</v>
       </c>
       <c r="M6" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$7="","",IFERROR(INDEX('Date actuale'!$D$6:$D$40,MATCH(A6,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1300</v>
+        <v>1420</v>
       </c>
       <c r="N6" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$7="","",IFERROR(INDEX('Date actuale'!$E$6:$E$40,MATCH(A6,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1300</v>
+        <v>1360</v>
       </c>
       <c r="O6" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$7="","",Sezoane!M7)</f>
@@ -25062,13 +25065,13 @@
         <v>229</v>
       </c>
       <c r="C6" s="48" t="n">
-        <v>900</v>
+        <v>1130</v>
       </c>
       <c r="D6" s="48" t="n">
-        <v>1480</v>
+        <v>920</v>
       </c>
       <c r="E6" s="48" t="n">
-        <v>1480</v>
+        <v>980</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>230</v>
@@ -25082,22 +25085,24 @@
         <v>231</v>
       </c>
       <c r="C7" s="48" t="n">
-        <v>1300</v>
+        <v>1580</v>
       </c>
       <c r="D7" s="48" t="n">
-        <v>1300</v>
+        <v>1420</v>
       </c>
       <c r="E7" s="48" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F7" s="38"/>
+        <v>1360</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="38" t="s">
         <v>65</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C8" s="48" t="n">
         <v>1500</v>
@@ -25115,7 +25120,7 @@
         <v>68</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C9" s="48" t="n">
         <v>1800</v>
@@ -25133,7 +25138,7 @@
         <v>69</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C10" s="48" t="n">
         <v>1350</v>
@@ -25151,7 +25156,7 @@
         <v>70</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C11" s="48" t="n">
         <v>1450</v>
@@ -25163,15 +25168,15 @@
         <v>1500</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C12" s="48" t="n">
         <v>900</v>
@@ -25183,7 +25188,7 @@
         <v>1380</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25204,7 +25209,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -25214,7 +25219,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
@@ -25224,7 +25229,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
@@ -25234,7 +25239,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="49" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
@@ -25244,7 +25249,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
@@ -25254,7 +25259,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -25264,7 +25269,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>

--- a/pricing/tarife.xlsx
+++ b/pricing/tarife.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="261">
   <si>
     <t xml:space="preserve">Strategia de prețuri – Travel Concept - Silver Mountain (A13)</t>
   </si>
@@ -851,6 +851,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.12 – 27.12.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setat 21.10.2026. Booking: doar planul „Sarbatori – Nerambursabil” deschis (1.890, min 3, Mobile rate 10% inclus în calcul); Airbnb min 3, politică „Fermă” (cea mai strictă disponibilă pe date), reducerea săptămânală 32% rămâne (risc acceptat); Travelminit min 3, politica „sarbatori”. Site 1.500, min 3, fără reduceri.</t>
   </si>
   <si>
     <t xml:space="preserve">28.12.2026 – 04.01.2027</t>
@@ -1867,41 +1870,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5332,7 +5335,7 @@
       </c>
       <c r="L7" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$8="","",IFERROR(INDEX('Date actuale'!$C$6:$C$40,MATCH(A7,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1500</v>
+        <v>1890</v>
       </c>
       <c r="M7" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$8="","",IFERROR(INDEX('Date actuale'!$D$6:$D$40,MATCH(A7,'Date actuale'!$A$6:$A$40,0)),""))</f>
@@ -5340,7 +5343,7 @@
       </c>
       <c r="N7" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$8="","",IFERROR(INDEX('Date actuale'!$E$6:$E$40,MATCH(A7,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1700</v>
+        <v>1630</v>
       </c>
       <c r="O7" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$8="","",Sezoane!M8)</f>
@@ -25105,22 +25108,24 @@
         <v>233</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>1500</v>
+        <v>1890</v>
       </c>
       <c r="D8" s="48" t="n">
         <v>1700</v>
       </c>
       <c r="E8" s="48" t="n">
-        <v>1700</v>
-      </c>
-      <c r="F8" s="38"/>
+        <v>1630</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="38" t="s">
         <v>68</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C9" s="48" t="n">
         <v>1800</v>
@@ -25138,7 +25143,7 @@
         <v>69</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C10" s="48" t="n">
         <v>1350</v>
@@ -25156,7 +25161,7 @@
         <v>70</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C11" s="48" t="n">
         <v>1450</v>
@@ -25168,15 +25173,15 @@
         <v>1500</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C12" s="48" t="n">
         <v>900</v>
@@ -25188,7 +25193,7 @@
         <v>1380</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25209,7 +25214,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -25219,7 +25224,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
@@ -25229,7 +25234,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
@@ -25239,7 +25244,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
@@ -25249,7 +25254,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
@@ -25259,7 +25264,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -25269,7 +25274,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>

--- a/pricing/tarife.xlsx
+++ b/pricing/tarife.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="262">
   <si>
     <t xml:space="preserve">Strategia de prețuri – Travel Concept - Silver Mountain (A13)</t>
   </si>
@@ -857,6 +857,9 @@
   </si>
   <si>
     <t xml:space="preserve">28.12.2026 – 04.01.2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setat 21.10.2026 (înainte: Booking 1.800, Airbnb 2.000/min 5, Travelminit 2.000). Booking: doar „Sarbatori – Nerambursabil” 2.270, min 4 (Mobile rate inclus în calcul); Airbnb 2.040, min 4, „Fermă”, reducerea săptămânală 32% rămâne (risc acceptat); Travelminit 1.960, min 4, politica „sarbatori”. Site 1.800, min 4, fără reduceri.</t>
   </si>
   <si>
     <t xml:space="preserve">05.01 – 14.02.2027</t>
@@ -1870,41 +1873,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5421,15 +5424,15 @@
       </c>
       <c r="L8" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$9="","",IFERROR(INDEX('Date actuale'!$C$6:$C$40,MATCH(A8,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1800</v>
+        <v>2270</v>
       </c>
       <c r="M8" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$9="","",IFERROR(INDEX('Date actuale'!$D$6:$D$40,MATCH(A8,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>2000</v>
+        <v>2040</v>
       </c>
       <c r="N8" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$9="","",IFERROR(INDEX('Date actuale'!$E$6:$E$40,MATCH(A8,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>2000</v>
+        <v>1960</v>
       </c>
       <c r="O8" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$9="","",Sezoane!M9)</f>
@@ -25128,22 +25131,24 @@
         <v>235</v>
       </c>
       <c r="C9" s="48" t="n">
-        <v>1800</v>
+        <v>2270</v>
       </c>
       <c r="D9" s="48" t="n">
-        <v>2000</v>
+        <v>2040</v>
       </c>
       <c r="E9" s="48" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F9" s="38"/>
+        <v>1960</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="38" t="s">
         <v>69</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C10" s="48" t="n">
         <v>1350</v>
@@ -25161,7 +25166,7 @@
         <v>70</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C11" s="48" t="n">
         <v>1450</v>
@@ -25173,15 +25178,15 @@
         <v>1500</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C12" s="48" t="n">
         <v>900</v>
@@ -25193,7 +25198,7 @@
         <v>1380</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25214,7 +25219,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -25224,7 +25229,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
@@ -25234,7 +25239,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
@@ -25244,7 +25249,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
@@ -25254,7 +25259,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
@@ -25264,7 +25269,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -25274,7 +25279,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>

--- a/pricing/tarife.xlsx
+++ b/pricing/tarife.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="263">
   <si>
     <t xml:space="preserve">Strategia de prețuri – Travel Concept - Silver Mountain (A13)</t>
   </si>
@@ -865,10 +865,13 @@
     <t xml:space="preserve">05.01 – 14.02.2027</t>
   </si>
   <si>
+    <t xml:space="preserve">Setat 21.10.2026 (înainte: Booking 1.350, Airbnb 1.450, Travelminit 1.450). Min 2 peste tot; Booking planuri 2–7 nopți −10…−33% (flexibile 14 zile). Site 1.350.</t>
+  </si>
+  <si>
     <t xml:space="preserve">15.02 – 07.03.2027</t>
   </si>
   <si>
-    <t xml:space="preserve">Airbnb are 1.500 doar până la 28.02; din 01.03 – 900</t>
+    <t xml:space="preserve">Setat 21.10.2026 (înainte: Booking 1.450, Airbnb 1.500 / 900 din 01.03, Travelminit 1.500). 20–21.02 ocupat (rezervare existentă, neatins). Site 1.450.</t>
   </si>
   <si>
     <t xml:space="preserve">(fără sezon pe site)</t>
@@ -877,7 +880,7 @@
     <t xml:space="preserve">08.03 – 30.04.2027</t>
   </si>
   <si>
-    <t xml:space="preserve">Site blocat; Airbnb 900 din 01.03; Travelminit 1.380</t>
+    <t xml:space="preserve">ANOMALIE de decis: site blocat (fără sezon), Booking/Airbnb 900, Travelminit 1.380; Travelminit fără reguli (min nopți/politică) din 08.03.</t>
   </si>
   <si>
     <t xml:space="preserve">Comisioane și setări observate</t>
@@ -1873,41 +1876,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5510,15 +5513,15 @@
       </c>
       <c r="L9" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$10="","",IFERROR(INDEX('Date actuale'!$C$6:$C$40,MATCH(A9,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1350</v>
+        <v>1700</v>
       </c>
       <c r="M9" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$10="","",IFERROR(INDEX('Date actuale'!$D$6:$D$40,MATCH(A9,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1450</v>
+        <v>1530</v>
       </c>
       <c r="N9" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$10="","",IFERROR(INDEX('Date actuale'!$E$6:$E$40,MATCH(A9,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1450</v>
+        <v>1470</v>
       </c>
       <c r="O9" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$10="","",Sezoane!M10)</f>
@@ -5596,15 +5599,15 @@
       </c>
       <c r="L10" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$11="","",IFERROR(INDEX('Date actuale'!$C$6:$C$40,MATCH(A10,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1450</v>
+        <v>1830</v>
       </c>
       <c r="M10" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$11="","",IFERROR(INDEX('Date actuale'!$D$6:$D$40,MATCH(A10,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1500</v>
+        <v>1640</v>
       </c>
       <c r="N10" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$11="","",IFERROR(INDEX('Date actuale'!$E$6:$E$40,MATCH(A10,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1500</v>
+        <v>1580</v>
       </c>
       <c r="O10" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$11="","",Sezoane!M11)</f>
@@ -25151,42 +25154,44 @@
         <v>237</v>
       </c>
       <c r="C10" s="48" t="n">
-        <v>1350</v>
+        <v>1700</v>
       </c>
       <c r="D10" s="48" t="n">
-        <v>1450</v>
+        <v>1530</v>
       </c>
       <c r="E10" s="48" t="n">
-        <v>1450</v>
-      </c>
-      <c r="F10" s="38"/>
+        <v>1470</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="38" t="s">
         <v>70</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C11" s="48" t="n">
-        <v>1450</v>
+        <v>1830</v>
       </c>
       <c r="D11" s="48" t="n">
-        <v>1500</v>
+        <v>1640</v>
       </c>
       <c r="E11" s="48" t="n">
-        <v>1500</v>
+        <v>1580</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C12" s="48" t="n">
         <v>900</v>
@@ -25198,7 +25203,7 @@
         <v>1380</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25219,7 +25224,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -25229,7 +25234,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
@@ -25239,7 +25244,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
@@ -25249,7 +25254,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
@@ -25259,7 +25264,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
@@ -25269,7 +25274,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -25279,7 +25284,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>

--- a/pricing/tarife.xlsx
+++ b/pricing/tarife.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="264">
   <si>
     <t xml:space="preserve">Strategia de prețuri – Travel Concept - Silver Mountain (A13)</t>
   </si>
@@ -348,7 +348,13 @@
     <t xml:space="preserve">Vacanta-schi-2027</t>
   </si>
   <si>
-    <t xml:space="preserve">După 07.03.2027 nu există sezon pe site → rezervări directe blocate</t>
+    <t xml:space="preserve">primavara-2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sezon primăvară</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adăugat 21.10.2026 (cerut de Mircea). După 30.06.2027 nu există sezon pe site → rezervări directe blocate</t>
   </si>
   <si>
     <t xml:space="preserve">Platforme – comisioane, reduceri automate, taxe</t>
@@ -874,13 +880,10 @@
     <t xml:space="preserve">Setat 21.10.2026 (înainte: Booking 1.450, Airbnb 1.500 / 900 din 01.03, Travelminit 1.500). 20–21.02 ocupat (rezervare existentă, neatins). Site 1.450.</t>
   </si>
   <si>
-    <t xml:space="preserve">(fără sezon pe site)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08.03 – 30.04.2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANOMALIE de decis: site blocat (fără sezon), Booking/Airbnb 900, Travelminit 1.380; Travelminit fără reguli (min nopți/politică) din 08.03.</t>
+    <t xml:space="preserve">08.03 – 30.06.2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Înainte de setare (21.10.2026): site blocat (fără sezon), Booking/Airbnb 900, Travelminit 1.380, Travelminit fără reguli din 08.03.</t>
   </si>
   <si>
     <t xml:space="preserve">Comisioane și setări observate</t>
@@ -1876,41 +1879,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K1" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2204,47 +2207,47 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!A12)</f>
-        <v/>
+        <v>primavara-2027</v>
       </c>
       <c r="B8" s="51" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!B12)</f>
-        <v/>
-      </c>
-      <c r="C8" s="52" t="str">
+        <v>Sezon primăvară</v>
+      </c>
+      <c r="C8" s="52" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!C12)</f>
-        <v/>
-      </c>
-      <c r="D8" s="52" t="str">
+        <v>46454</v>
+      </c>
+      <c r="D8" s="52" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!D12)</f>
-        <v/>
-      </c>
-      <c r="E8" s="51" t="str">
+        <v>46568</v>
+      </c>
+      <c r="E8" s="53" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!E12)</f>
-        <v/>
-      </c>
-      <c r="F8" s="54" t="str">
+        <v>900</v>
+      </c>
+      <c r="F8" s="54" t="n">
         <f aca="false">IF(OR(Sezoane!$A$12="",2&lt;Sezoane!$F12),"",IF(2=Sezoane!$F12,N(Sezoane!G12),IF(N(Sezoane!G12)&gt;0,Sezoane!G12,"")))</f>
-        <v/>
-      </c>
-      <c r="G8" s="54" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="54" t="n">
         <f aca="false">IF(OR(Sezoane!$A$12="",3&lt;Sezoane!$F12),"",IF(3=Sezoane!$F12,N(Sezoane!H12),IF(N(Sezoane!H12)&gt;0,Sezoane!H12,"")))</f>
-        <v/>
-      </c>
-      <c r="H8" s="54" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="H8" s="54" t="n">
         <f aca="false">IF(OR(Sezoane!$A$12="",4&lt;Sezoane!$F12),"",IF(4=Sezoane!$F12,N(Sezoane!I12),IF(N(Sezoane!I12)&gt;0,Sezoane!I12,"")))</f>
-        <v/>
-      </c>
-      <c r="I8" s="54" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="54" t="n">
         <f aca="false">IF(OR(Sezoane!$A$12="",5&lt;Sezoane!$F12),"",IF(5=Sezoane!$F12,N(Sezoane!J12),IF(N(Sezoane!J12)&gt;0,Sezoane!J12,"")))</f>
-        <v/>
-      </c>
-      <c r="J8" s="54" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="J8" s="54" t="n">
         <f aca="false">IF(OR(Sezoane!$A$12="",6&lt;Sezoane!$F12),"",IF(6=Sezoane!$F12,N(Sezoane!K12),IF(N(Sezoane!K12)&gt;0,Sezoane!K12,"")))</f>
-        <v/>
-      </c>
-      <c r="K8" s="54" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="K8" s="54" t="n">
         <f aca="false">IF(OR(Sezoane!$A$12="",7&lt;Sezoane!$F12),"",IF(7=Sezoane!$F12,N(Sezoane!L12),IF(N(Sezoane!L12)&gt;0,Sezoane!L12,"")))</f>
-        <v/>
+        <v>0.33</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -3986,26 +3989,52 @@
       <c r="M11" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="11"/>
+      <c r="O11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="O11" s="13"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>46454</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L12" s="15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="O12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4522,7 +4551,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4532,7 +4561,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4550,7 +4579,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4560,7 +4589,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>7</v>
@@ -4572,7 +4601,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>5</v>
@@ -4584,7 +4613,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>4</v>
@@ -4596,7 +4625,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">(B5+B6)*B7</f>
@@ -4617,27 +4646,27 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>0</v>
@@ -4652,12 +4681,12 @@
         <v>0.12</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B12" s="20" t="n">
         <v>0</v>
@@ -4672,12 +4701,12 @@
         <v>0</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B13" s="14" t="n">
         <v>1</v>
@@ -4692,12 +4721,12 @@
         <v>0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B14" s="20" t="n">
         <v>0</v>
@@ -4712,12 +4741,12 @@
         <v>0</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B15" s="14" t="n">
         <v>0</v>
@@ -4732,12 +4761,12 @@
         <v>1</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B16" s="13" t="n">
         <v>10</v>
@@ -4752,12 +4781,12 @@
         <v>10</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B17" s="14" t="n">
         <v>1</v>
@@ -4772,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4785,7 +4814,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -4795,13 +4824,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B20" s="22" t="n">
         <v>0.33</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -4809,7 +4838,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B21" s="22" t="n">
         <v>0.33</v>
@@ -4829,7 +4858,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">1-(1-B11)*(1-B12)</f>
@@ -4859,7 +4888,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -4869,13 +4898,13 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B26" s="15" t="n">
         <v>0.3</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
@@ -4883,13 +4912,13 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B27" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
@@ -4897,13 +4926,13 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B28" s="15" t="n">
         <v>0.15</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="24"/>
@@ -4919,7 +4948,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -4929,13 +4958,13 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B31" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
@@ -4986,7 +5015,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5011,7 +5040,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5062,64 +5091,64 @@
         <v>45</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5641,87 +5670,87 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!A12)</f>
-        <v/>
-      </c>
-      <c r="B11" s="26" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="B11" s="26" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!C12)</f>
-        <v/>
-      </c>
-      <c r="C11" s="26" t="str">
+        <v>46454</v>
+      </c>
+      <c r="C11" s="26" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!D12)</f>
-        <v/>
-      </c>
-      <c r="D11" s="25" t="str">
+        <v>46568</v>
+      </c>
+      <c r="D11" s="27" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!F12)</f>
-        <v/>
-      </c>
-      <c r="E11" s="28" t="str">
+        <v>2</v>
+      </c>
+      <c r="E11" s="28" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!E12)</f>
-        <v/>
-      </c>
-      <c r="F11" s="29" t="str">
+        <v>900</v>
+      </c>
+      <c r="F11" s="29" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",CEILING(IF(Platforme!$C$13=1,(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*1/(1+Platforme!$B$31))/(1-(Platforme!$C$11+Platforme!$C$12-Platforme!$C$11*Platforme!$C$12))+Platforme!$B$8)/(1-(Platforme!$C$14*Platforme!$C$15)),(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*1/(1+Platforme!$B$31))+Platforme!$B$8)/((1-(Platforme!$C$11+Platforme!$C$12-Platforme!$C$11*Platforme!$C$12))*(1-(Platforme!$C$14*Platforme!$C$15)))),Platforme!$C$16))</f>
-        <v/>
-      </c>
-      <c r="G11" s="29" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G11" s="29" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IF(N(Sezoane!O12)=0,CEILING(IF(Platforme!$D$13=1,(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*1/(1+Platforme!$B$31))/(1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12))+Platforme!$B$8)/(1-(Platforme!$D$14*Platforme!$D$15)),(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*1/(1+Platforme!$B$31))+Platforme!$B$8)/((1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12))*(1-(Platforme!$D$14*Platforme!$D$15)))),Platforme!$D$16),MAX(CEILING(IF(Platforme!$D$13=1,(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*Platforme!$B$27*(1+Platforme!$B$31)/(1+Platforme!$B$31))/(1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12))+Platforme!$B$8)/(1-(Platforme!$D$14*Platforme!$D$15)),(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*Platforme!$B$27*(1+Platforme!$B$31)/(1+Platforme!$B$31))+Platforme!$B$8)/((1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12))*(1-(Platforme!$D$14*Platforme!$D$15)))),Platforme!$D$16),CEILING(CEILING(IF(Platforme!$D$13=1,(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*1/(1+Platforme!$B$31))/(1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12))+Platforme!$B$8)/(1-(Platforme!$D$14*Platforme!$D$15)),(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*1/(1+Platforme!$B$31))+Platforme!$B$8)/((1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12))*(1-(Platforme!$D$14*Platforme!$D$15)))),Platforme!$D$16)*(1-Platforme!$B$26)+Sezoane!O12*Platforme!$B$26,Platforme!$D$16))))</f>
-        <v/>
-      </c>
-      <c r="H11" s="29" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H11" s="29" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",CEILING(IF(Platforme!$E$13=1,(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*1/(1+Platforme!$B$31))/(1-(Platforme!$E$11+Platforme!$E$12-Platforme!$E$11*Platforme!$E$12))+Platforme!$B$8)/(1-(Platforme!$E$14*Platforme!$E$15)),(((Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12))*1/(1+Platforme!$B$31))+Platforme!$B$8)/((1-(Platforme!$E$11+Platforme!$E$12-Platforme!$E$11*Platforme!$E$12))*(1-(Platforme!$E$14*Platforme!$E$15)))),Platforme!$E$16))</f>
-        <v/>
-      </c>
-      <c r="I11" s="30" t="str">
+        <v>980</v>
+      </c>
+      <c r="I11" s="30" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",(Sezoane!E12-Platforme!$B$8)*(1-(Platforme!$B$11+Platforme!$B$12-Platforme!$B$11*Platforme!$B$12)))</f>
-        <v/>
-      </c>
-      <c r="J11" s="30" t="str">
+        <v>852</v>
+      </c>
+      <c r="J11" s="30" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",F11*(1-Platforme!$C$14))</f>
-        <v/>
-      </c>
-      <c r="K11" s="31" t="str">
+        <v>1017</v>
+      </c>
+      <c r="K11" s="31" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",1-E11/MIN(J11,G11,H11))</f>
-        <v/>
-      </c>
-      <c r="L11" s="32" t="str">
+        <v>0.0816326530612245</v>
+      </c>
+      <c r="L11" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IFERROR(INDEX('Date actuale'!$C$6:$C$40,MATCH(A11,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v/>
-      </c>
-      <c r="M11" s="32" t="str">
+        <v>900</v>
+      </c>
+      <c r="M11" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IFERROR(INDEX('Date actuale'!$D$6:$D$40,MATCH(A11,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v/>
-      </c>
-      <c r="N11" s="32" t="str">
+        <v>900</v>
+      </c>
+      <c r="N11" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IFERROR(INDEX('Date actuale'!$E$6:$E$40,MATCH(A11,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v/>
+        <v>1380</v>
       </c>
       <c r="O11" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!M12)</f>
-        <v/>
+        <v>Flexibil 14 zile</v>
       </c>
       <c r="P11" s="28" t="str">
         <f aca="false">IF(OR(Sezoane!$A$12="",N(Sezoane!O12)=0),"",Sezoane!O12)</f>
         <v/>
       </c>
-      <c r="Q11" s="30" t="str">
+      <c r="Q11" s="30" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IF(Platforme!$D$13=1,(G11*(1-Platforme!$D$14)-Platforme!$B$8)*(1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12)),G11*(1-Platforme!$D$14)*(1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12))-Platforme!$B$8))</f>
-        <v/>
-      </c>
-      <c r="R11" s="31" t="str">
+        <v>813.9</v>
+      </c>
+      <c r="R11" s="31" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Q11/U11-1)</f>
-        <v/>
-      </c>
-      <c r="S11" s="30" t="str">
+        <v>0.00304577464788736</v>
+      </c>
+      <c r="S11" s="30" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",G11*(1-Platforme!$B$28))</f>
-        <v/>
-      </c>
-      <c r="T11" s="30" t="str">
+        <v>867</v>
+      </c>
+      <c r="T11" s="30" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IF(Platforme!$D$13=1,(S11*(1-Platforme!$D$14)-Platforme!$B$8)*(1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12)),S11*(1-Platforme!$D$14)*(1-(Platforme!$D$11+Platforme!$D$12-Platforme!$D$11*Platforme!$D$12))-Platforme!$B$8))</f>
-        <v/>
-      </c>
-      <c r="U11" s="33" t="str">
+        <v>684.615</v>
+      </c>
+      <c r="U11" s="33" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",I11/(1+Platforme!$B$31))</f>
-        <v/>
+        <v>811.428571428571</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8184,7 +8213,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8196,7 +8225,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8218,7 +8247,7 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>46402</v>
@@ -8226,28 +8255,28 @@
       <c r="C4" s="2"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E5" s="30" t="n">
         <f aca="false">SUM(D20:D49)</f>
@@ -8268,14 +8297,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E6" s="30" t="n">
         <f aca="false">-E5*IF(Platforme!B17=1,$B$11,0)</f>
@@ -8296,14 +8325,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E7" s="30" t="n">
         <f aca="false">-(E5+E6)*Platforme!B14</f>
@@ -8324,7 +8353,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B8" s="34" t="n">
         <f aca="false">B4+B5</f>
@@ -8332,7 +8361,7 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E8" s="29" t="n">
         <f aca="false">E5+E6+E7</f>
@@ -8353,7 +8382,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B9" s="35" t="str">
         <f aca="false">IFERROR(INDEX(Sezoane!$A$6:$A$40,MATCH(B4,Sezoane!$C$6:$C$40,1)),"")</f>
@@ -8361,7 +8390,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E9" s="30" t="n">
         <f aca="false">(Platforme!$B$5+Platforme!$B$6)*$B$6*$B$5</f>
@@ -8382,7 +8411,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B10" s="36" t="n">
         <f aca="false">IFERROR(INDEX(Sezoane!$F$6:$F$40,MATCH(B4,Sezoane!$C$6:$C$40,1)),"")</f>
@@ -8390,7 +8419,7 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E10" s="30" t="n">
         <f aca="false">-IF(Platforme!B13=1,E8-E9,E8)*(Platforme!B11+Platforme!B12-Platforme!B11*Platforme!B12)</f>
@@ -8411,7 +8440,7 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B11" s="23" t="n">
         <f aca="false">IFERROR(IF(B5&lt;B10,0,N(INDEX(Sezoane!$G$6:$L$40,MATCH(B4,Sezoane!$C$6:$C$40,1),MIN(B5,7)-1))),0)</f>
@@ -8419,7 +8448,7 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E11" s="29" t="n">
         <f aca="false">E8-E9+E10</f>
@@ -8440,7 +8469,7 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">IF(B5&gt;=28,Platforme!B21,IF(B5&gt;=7,Platforme!B20,0))</f>
@@ -8448,7 +8477,7 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="30" t="n">
@@ -8466,7 +8495,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13" s="37" t="str">
         <f aca="false">IF(B9="","⚠ Data nu e în niciun sezon – pe site rezervarea e blocată",IF(B5&lt;B10,"⚠ Sub numărul minim de nopți","OK"))</f>
@@ -8521,7 +8550,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -8533,25 +8562,25 @@
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H19" s="2"/>
     </row>
@@ -9513,7 +9542,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9526,7 +9555,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B2" s="40" t="n">
         <v>46316</v>
@@ -9552,31 +9581,31 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14834,31 +14863,31 @@
       </c>
       <c r="C143" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A143,Sezoane!$C$6:$C$40,1)),A143&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A143,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A143,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D143" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D143" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A143,Sezoane!$C$6:$C$40,1)),A143&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A143,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A143,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E143" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E143" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A143,Sezoane!$C$6:$C$40,1)),A143&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A143,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A143,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F143" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F143" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A143,Sezoane!$C$6:$C$40,1)),A143&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A143,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A143,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G143" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G143" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A143,Sezoane!$C$6:$C$40,1)),A143&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A143,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A143,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H143" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H143" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A143,Sezoane!$C$6:$C$40,1)),A143&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A143,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A143,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I143" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I143" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A143,Sezoane!$C$6:$C$40,1)),A143&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A143,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A143,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14872,31 +14901,31 @@
       </c>
       <c r="C144" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A144,Sezoane!$C$6:$C$40,1)),A144&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A144,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A144,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D144" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D144" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A144,Sezoane!$C$6:$C$40,1)),A144&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A144,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A144,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E144" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E144" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A144,Sezoane!$C$6:$C$40,1)),A144&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A144,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A144,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F144" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F144" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A144,Sezoane!$C$6:$C$40,1)),A144&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A144,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A144,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G144" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G144" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A144,Sezoane!$C$6:$C$40,1)),A144&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A144,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A144,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H144" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H144" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A144,Sezoane!$C$6:$C$40,1)),A144&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A144,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A144,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I144" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I144" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A144,Sezoane!$C$6:$C$40,1)),A144&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A144,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A144,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14910,31 +14939,31 @@
       </c>
       <c r="C145" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A145,Sezoane!$C$6:$C$40,1)),A145&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A145,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A145,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D145" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D145" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A145,Sezoane!$C$6:$C$40,1)),A145&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A145,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A145,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E145" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E145" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A145,Sezoane!$C$6:$C$40,1)),A145&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A145,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A145,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F145" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F145" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A145,Sezoane!$C$6:$C$40,1)),A145&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A145,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A145,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G145" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G145" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A145,Sezoane!$C$6:$C$40,1)),A145&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A145,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A145,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H145" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H145" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A145,Sezoane!$C$6:$C$40,1)),A145&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A145,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A145,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I145" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I145" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A145,Sezoane!$C$6:$C$40,1)),A145&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A145,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A145,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14948,31 +14977,31 @@
       </c>
       <c r="C146" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A146,Sezoane!$C$6:$C$40,1)),A146&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A146,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A146,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D146" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D146" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A146,Sezoane!$C$6:$C$40,1)),A146&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A146,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A146,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E146" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E146" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A146,Sezoane!$C$6:$C$40,1)),A146&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A146,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A146,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F146" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F146" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A146,Sezoane!$C$6:$C$40,1)),A146&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A146,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A146,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G146" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G146" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A146,Sezoane!$C$6:$C$40,1)),A146&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A146,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A146,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H146" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H146" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A146,Sezoane!$C$6:$C$40,1)),A146&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A146,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A146,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I146" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I146" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A146,Sezoane!$C$6:$C$40,1)),A146&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A146,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A146,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14986,31 +15015,31 @@
       </c>
       <c r="C147" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A147,Sezoane!$C$6:$C$40,1)),A147&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A147,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A147,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D147" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D147" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A147,Sezoane!$C$6:$C$40,1)),A147&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A147,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A147,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E147" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E147" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A147,Sezoane!$C$6:$C$40,1)),A147&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A147,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A147,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F147" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F147" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A147,Sezoane!$C$6:$C$40,1)),A147&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A147,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A147,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G147" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G147" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A147,Sezoane!$C$6:$C$40,1)),A147&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A147,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A147,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H147" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H147" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A147,Sezoane!$C$6:$C$40,1)),A147&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A147,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A147,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I147" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I147" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A147,Sezoane!$C$6:$C$40,1)),A147&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A147,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A147,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15024,31 +15053,31 @@
       </c>
       <c r="C148" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A148,Sezoane!$C$6:$C$40,1)),A148&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A148,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A148,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D148" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D148" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A148,Sezoane!$C$6:$C$40,1)),A148&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A148,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A148,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E148" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E148" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A148,Sezoane!$C$6:$C$40,1)),A148&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A148,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A148,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F148" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F148" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A148,Sezoane!$C$6:$C$40,1)),A148&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A148,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A148,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G148" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G148" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A148,Sezoane!$C$6:$C$40,1)),A148&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A148,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A148,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H148" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H148" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A148,Sezoane!$C$6:$C$40,1)),A148&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A148,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A148,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I148" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I148" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A148,Sezoane!$C$6:$C$40,1)),A148&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A148,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A148,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15062,31 +15091,31 @@
       </c>
       <c r="C149" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A149,Sezoane!$C$6:$C$40,1)),A149&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A149,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A149,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D149" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D149" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A149,Sezoane!$C$6:$C$40,1)),A149&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A149,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A149,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E149" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E149" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A149,Sezoane!$C$6:$C$40,1)),A149&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A149,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A149,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F149" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F149" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A149,Sezoane!$C$6:$C$40,1)),A149&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A149,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A149,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G149" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G149" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A149,Sezoane!$C$6:$C$40,1)),A149&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A149,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A149,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H149" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H149" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A149,Sezoane!$C$6:$C$40,1)),A149&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A149,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A149,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I149" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I149" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A149,Sezoane!$C$6:$C$40,1)),A149&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A149,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A149,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15100,31 +15129,31 @@
       </c>
       <c r="C150" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A150,Sezoane!$C$6:$C$40,1)),A150&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A150,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A150,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D150" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D150" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A150,Sezoane!$C$6:$C$40,1)),A150&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A150,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A150,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E150" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E150" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A150,Sezoane!$C$6:$C$40,1)),A150&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A150,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A150,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F150" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F150" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A150,Sezoane!$C$6:$C$40,1)),A150&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A150,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A150,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G150" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G150" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A150,Sezoane!$C$6:$C$40,1)),A150&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A150,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A150,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H150" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H150" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A150,Sezoane!$C$6:$C$40,1)),A150&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A150,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A150,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I150" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I150" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A150,Sezoane!$C$6:$C$40,1)),A150&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A150,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A150,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15138,31 +15167,31 @@
       </c>
       <c r="C151" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A151,Sezoane!$C$6:$C$40,1)),A151&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A151,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A151,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D151" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D151" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A151,Sezoane!$C$6:$C$40,1)),A151&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A151,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A151,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E151" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E151" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A151,Sezoane!$C$6:$C$40,1)),A151&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A151,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A151,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F151" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F151" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A151,Sezoane!$C$6:$C$40,1)),A151&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A151,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A151,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G151" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G151" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A151,Sezoane!$C$6:$C$40,1)),A151&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A151,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A151,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H151" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H151" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A151,Sezoane!$C$6:$C$40,1)),A151&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A151,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A151,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I151" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I151" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A151,Sezoane!$C$6:$C$40,1)),A151&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A151,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A151,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15176,31 +15205,31 @@
       </c>
       <c r="C152" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A152,Sezoane!$C$6:$C$40,1)),A152&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A152,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A152,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D152" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D152" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A152,Sezoane!$C$6:$C$40,1)),A152&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A152,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A152,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E152" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E152" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A152,Sezoane!$C$6:$C$40,1)),A152&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A152,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A152,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F152" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F152" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A152,Sezoane!$C$6:$C$40,1)),A152&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A152,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A152,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G152" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G152" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A152,Sezoane!$C$6:$C$40,1)),A152&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A152,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A152,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H152" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H152" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A152,Sezoane!$C$6:$C$40,1)),A152&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A152,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A152,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I152" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I152" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A152,Sezoane!$C$6:$C$40,1)),A152&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A152,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A152,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15214,31 +15243,31 @@
       </c>
       <c r="C153" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A153,Sezoane!$C$6:$C$40,1)),A153&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A153,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A153,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D153" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D153" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A153,Sezoane!$C$6:$C$40,1)),A153&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A153,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A153,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E153" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E153" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A153,Sezoane!$C$6:$C$40,1)),A153&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A153,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A153,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F153" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F153" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A153,Sezoane!$C$6:$C$40,1)),A153&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A153,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A153,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G153" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G153" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A153,Sezoane!$C$6:$C$40,1)),A153&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A153,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A153,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H153" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H153" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A153,Sezoane!$C$6:$C$40,1)),A153&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A153,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A153,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I153" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I153" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A153,Sezoane!$C$6:$C$40,1)),A153&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A153,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A153,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15252,31 +15281,31 @@
       </c>
       <c r="C154" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A154,Sezoane!$C$6:$C$40,1)),A154&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A154,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A154,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D154" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D154" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A154,Sezoane!$C$6:$C$40,1)),A154&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A154,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A154,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E154" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E154" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A154,Sezoane!$C$6:$C$40,1)),A154&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A154,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A154,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F154" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F154" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A154,Sezoane!$C$6:$C$40,1)),A154&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A154,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A154,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G154" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G154" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A154,Sezoane!$C$6:$C$40,1)),A154&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A154,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A154,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H154" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H154" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A154,Sezoane!$C$6:$C$40,1)),A154&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A154,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A154,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I154" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I154" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A154,Sezoane!$C$6:$C$40,1)),A154&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A154,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A154,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15290,31 +15319,31 @@
       </c>
       <c r="C155" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A155,Sezoane!$C$6:$C$40,1)),A155&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A155,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A155,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D155" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D155" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A155,Sezoane!$C$6:$C$40,1)),A155&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A155,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A155,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E155" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E155" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A155,Sezoane!$C$6:$C$40,1)),A155&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A155,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A155,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F155" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F155" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A155,Sezoane!$C$6:$C$40,1)),A155&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A155,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A155,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G155" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G155" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A155,Sezoane!$C$6:$C$40,1)),A155&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A155,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A155,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H155" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H155" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A155,Sezoane!$C$6:$C$40,1)),A155&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A155,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A155,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I155" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I155" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A155,Sezoane!$C$6:$C$40,1)),A155&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A155,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A155,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15328,31 +15357,31 @@
       </c>
       <c r="C156" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A156,Sezoane!$C$6:$C$40,1)),A156&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A156,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A156,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D156" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D156" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A156,Sezoane!$C$6:$C$40,1)),A156&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A156,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A156,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E156" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E156" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A156,Sezoane!$C$6:$C$40,1)),A156&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A156,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A156,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F156" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F156" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A156,Sezoane!$C$6:$C$40,1)),A156&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A156,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A156,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G156" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G156" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A156,Sezoane!$C$6:$C$40,1)),A156&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A156,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A156,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H156" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H156" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A156,Sezoane!$C$6:$C$40,1)),A156&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A156,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A156,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I156" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I156" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A156,Sezoane!$C$6:$C$40,1)),A156&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A156,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A156,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15366,31 +15395,31 @@
       </c>
       <c r="C157" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A157,Sezoane!$C$6:$C$40,1)),A157&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A157,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A157,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D157" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D157" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A157,Sezoane!$C$6:$C$40,1)),A157&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A157,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A157,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E157" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E157" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A157,Sezoane!$C$6:$C$40,1)),A157&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A157,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A157,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F157" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F157" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A157,Sezoane!$C$6:$C$40,1)),A157&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A157,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A157,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G157" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G157" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A157,Sezoane!$C$6:$C$40,1)),A157&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A157,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A157,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H157" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H157" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A157,Sezoane!$C$6:$C$40,1)),A157&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A157,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A157,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I157" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I157" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A157,Sezoane!$C$6:$C$40,1)),A157&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A157,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A157,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15404,31 +15433,31 @@
       </c>
       <c r="C158" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A158,Sezoane!$C$6:$C$40,1)),A158&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A158,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A158,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D158" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D158" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A158,Sezoane!$C$6:$C$40,1)),A158&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A158,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A158,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E158" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E158" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A158,Sezoane!$C$6:$C$40,1)),A158&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A158,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A158,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F158" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F158" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A158,Sezoane!$C$6:$C$40,1)),A158&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A158,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A158,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G158" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G158" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A158,Sezoane!$C$6:$C$40,1)),A158&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A158,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A158,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H158" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H158" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A158,Sezoane!$C$6:$C$40,1)),A158&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A158,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A158,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I158" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I158" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A158,Sezoane!$C$6:$C$40,1)),A158&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A158,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A158,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15442,31 +15471,31 @@
       </c>
       <c r="C159" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A159,Sezoane!$C$6:$C$40,1)),A159&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A159,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A159,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D159" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D159" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A159,Sezoane!$C$6:$C$40,1)),A159&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A159,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A159,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E159" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E159" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A159,Sezoane!$C$6:$C$40,1)),A159&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A159,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A159,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F159" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F159" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A159,Sezoane!$C$6:$C$40,1)),A159&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A159,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A159,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G159" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G159" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A159,Sezoane!$C$6:$C$40,1)),A159&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A159,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A159,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H159" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H159" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A159,Sezoane!$C$6:$C$40,1)),A159&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A159,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A159,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I159" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I159" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A159,Sezoane!$C$6:$C$40,1)),A159&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A159,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A159,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15480,31 +15509,31 @@
       </c>
       <c r="C160" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A160,Sezoane!$C$6:$C$40,1)),A160&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A160,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A160,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D160" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D160" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A160,Sezoane!$C$6:$C$40,1)),A160&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A160,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A160,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E160" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E160" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A160,Sezoane!$C$6:$C$40,1)),A160&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A160,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A160,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F160" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F160" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A160,Sezoane!$C$6:$C$40,1)),A160&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A160,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A160,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G160" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G160" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A160,Sezoane!$C$6:$C$40,1)),A160&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A160,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A160,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H160" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H160" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A160,Sezoane!$C$6:$C$40,1)),A160&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A160,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A160,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I160" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I160" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A160,Sezoane!$C$6:$C$40,1)),A160&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A160,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A160,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15518,31 +15547,31 @@
       </c>
       <c r="C161" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A161,Sezoane!$C$6:$C$40,1)),A161&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A161,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A161,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D161" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D161" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A161,Sezoane!$C$6:$C$40,1)),A161&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A161,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A161,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E161" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E161" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A161,Sezoane!$C$6:$C$40,1)),A161&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A161,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A161,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F161" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F161" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A161,Sezoane!$C$6:$C$40,1)),A161&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A161,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A161,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G161" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G161" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A161,Sezoane!$C$6:$C$40,1)),A161&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A161,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A161,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H161" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H161" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A161,Sezoane!$C$6:$C$40,1)),A161&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A161,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A161,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I161" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I161" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A161,Sezoane!$C$6:$C$40,1)),A161&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A161,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A161,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15556,31 +15585,31 @@
       </c>
       <c r="C162" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A162,Sezoane!$C$6:$C$40,1)),A162&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A162,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A162,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D162" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D162" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A162,Sezoane!$C$6:$C$40,1)),A162&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A162,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A162,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E162" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E162" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A162,Sezoane!$C$6:$C$40,1)),A162&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A162,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A162,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F162" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F162" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A162,Sezoane!$C$6:$C$40,1)),A162&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A162,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A162,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G162" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G162" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A162,Sezoane!$C$6:$C$40,1)),A162&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A162,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A162,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H162" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H162" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A162,Sezoane!$C$6:$C$40,1)),A162&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A162,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A162,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I162" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I162" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A162,Sezoane!$C$6:$C$40,1)),A162&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A162,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A162,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15594,31 +15623,31 @@
       </c>
       <c r="C163" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A163,Sezoane!$C$6:$C$40,1)),A163&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A163,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A163,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D163" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D163" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A163,Sezoane!$C$6:$C$40,1)),A163&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A163,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A163,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E163" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E163" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A163,Sezoane!$C$6:$C$40,1)),A163&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A163,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A163,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F163" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F163" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A163,Sezoane!$C$6:$C$40,1)),A163&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A163,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A163,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G163" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G163" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A163,Sezoane!$C$6:$C$40,1)),A163&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A163,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A163,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H163" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H163" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A163,Sezoane!$C$6:$C$40,1)),A163&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A163,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A163,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I163" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I163" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A163,Sezoane!$C$6:$C$40,1)),A163&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A163,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A163,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15632,31 +15661,31 @@
       </c>
       <c r="C164" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A164,Sezoane!$C$6:$C$40,1)),A164&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A164,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A164,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D164" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D164" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A164,Sezoane!$C$6:$C$40,1)),A164&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A164,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A164,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E164" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E164" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A164,Sezoane!$C$6:$C$40,1)),A164&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A164,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A164,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F164" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F164" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A164,Sezoane!$C$6:$C$40,1)),A164&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A164,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A164,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G164" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G164" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A164,Sezoane!$C$6:$C$40,1)),A164&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A164,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A164,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H164" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H164" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A164,Sezoane!$C$6:$C$40,1)),A164&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A164,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A164,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I164" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I164" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A164,Sezoane!$C$6:$C$40,1)),A164&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A164,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A164,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15670,31 +15699,31 @@
       </c>
       <c r="C165" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A165,Sezoane!$C$6:$C$40,1)),A165&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A165,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A165,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D165" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D165" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A165,Sezoane!$C$6:$C$40,1)),A165&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A165,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A165,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E165" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E165" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A165,Sezoane!$C$6:$C$40,1)),A165&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A165,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A165,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F165" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F165" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A165,Sezoane!$C$6:$C$40,1)),A165&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A165,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A165,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G165" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G165" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A165,Sezoane!$C$6:$C$40,1)),A165&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A165,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A165,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H165" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H165" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A165,Sezoane!$C$6:$C$40,1)),A165&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A165,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A165,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I165" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I165" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A165,Sezoane!$C$6:$C$40,1)),A165&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A165,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A165,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15708,31 +15737,31 @@
       </c>
       <c r="C166" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A166,Sezoane!$C$6:$C$40,1)),A166&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A166,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A166,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D166" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D166" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A166,Sezoane!$C$6:$C$40,1)),A166&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A166,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A166,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E166" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E166" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A166,Sezoane!$C$6:$C$40,1)),A166&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A166,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A166,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F166" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F166" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A166,Sezoane!$C$6:$C$40,1)),A166&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A166,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A166,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G166" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G166" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A166,Sezoane!$C$6:$C$40,1)),A166&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A166,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A166,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H166" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H166" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A166,Sezoane!$C$6:$C$40,1)),A166&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A166,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A166,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I166" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I166" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A166,Sezoane!$C$6:$C$40,1)),A166&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A166,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A166,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15746,31 +15775,31 @@
       </c>
       <c r="C167" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A167,Sezoane!$C$6:$C$40,1)),A167&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A167,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A167,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D167" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D167" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A167,Sezoane!$C$6:$C$40,1)),A167&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A167,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A167,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E167" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E167" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A167,Sezoane!$C$6:$C$40,1)),A167&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A167,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A167,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F167" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F167" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A167,Sezoane!$C$6:$C$40,1)),A167&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A167,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A167,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G167" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G167" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A167,Sezoane!$C$6:$C$40,1)),A167&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A167,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A167,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H167" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H167" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A167,Sezoane!$C$6:$C$40,1)),A167&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A167,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A167,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I167" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I167" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A167,Sezoane!$C$6:$C$40,1)),A167&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A167,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A167,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15784,31 +15813,31 @@
       </c>
       <c r="C168" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A168,Sezoane!$C$6:$C$40,1)),A168&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A168,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A168,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D168" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D168" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A168,Sezoane!$C$6:$C$40,1)),A168&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A168,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A168,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E168" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E168" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A168,Sezoane!$C$6:$C$40,1)),A168&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A168,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A168,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F168" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F168" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A168,Sezoane!$C$6:$C$40,1)),A168&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A168,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A168,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G168" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G168" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A168,Sezoane!$C$6:$C$40,1)),A168&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A168,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A168,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H168" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H168" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A168,Sezoane!$C$6:$C$40,1)),A168&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A168,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A168,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I168" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I168" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A168,Sezoane!$C$6:$C$40,1)),A168&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A168,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A168,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15822,31 +15851,31 @@
       </c>
       <c r="C169" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A169,Sezoane!$C$6:$C$40,1)),A169&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A169,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A169,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D169" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D169" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A169,Sezoane!$C$6:$C$40,1)),A169&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A169,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A169,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E169" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E169" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A169,Sezoane!$C$6:$C$40,1)),A169&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A169,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A169,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F169" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F169" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A169,Sezoane!$C$6:$C$40,1)),A169&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A169,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A169,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G169" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G169" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A169,Sezoane!$C$6:$C$40,1)),A169&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A169,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A169,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H169" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H169" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A169,Sezoane!$C$6:$C$40,1)),A169&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A169,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A169,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I169" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I169" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A169,Sezoane!$C$6:$C$40,1)),A169&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A169,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A169,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15860,31 +15889,31 @@
       </c>
       <c r="C170" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A170,Sezoane!$C$6:$C$40,1)),A170&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A170,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A170,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D170" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D170" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A170,Sezoane!$C$6:$C$40,1)),A170&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A170,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A170,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E170" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E170" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A170,Sezoane!$C$6:$C$40,1)),A170&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A170,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A170,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F170" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F170" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A170,Sezoane!$C$6:$C$40,1)),A170&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A170,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A170,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G170" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G170" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A170,Sezoane!$C$6:$C$40,1)),A170&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A170,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A170,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H170" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H170" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A170,Sezoane!$C$6:$C$40,1)),A170&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A170,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A170,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I170" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I170" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A170,Sezoane!$C$6:$C$40,1)),A170&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A170,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A170,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15898,31 +15927,31 @@
       </c>
       <c r="C171" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A171,Sezoane!$C$6:$C$40,1)),A171&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A171,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A171,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D171" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D171" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A171,Sezoane!$C$6:$C$40,1)),A171&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A171,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A171,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E171" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E171" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A171,Sezoane!$C$6:$C$40,1)),A171&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A171,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A171,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F171" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F171" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A171,Sezoane!$C$6:$C$40,1)),A171&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A171,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A171,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G171" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G171" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A171,Sezoane!$C$6:$C$40,1)),A171&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A171,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A171,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H171" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H171" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A171,Sezoane!$C$6:$C$40,1)),A171&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A171,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A171,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I171" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I171" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A171,Sezoane!$C$6:$C$40,1)),A171&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A171,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A171,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15936,31 +15965,31 @@
       </c>
       <c r="C172" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A172,Sezoane!$C$6:$C$40,1)),A172&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A172,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A172,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D172" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D172" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A172,Sezoane!$C$6:$C$40,1)),A172&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A172,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A172,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E172" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E172" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A172,Sezoane!$C$6:$C$40,1)),A172&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A172,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A172,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F172" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F172" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A172,Sezoane!$C$6:$C$40,1)),A172&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A172,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A172,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G172" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G172" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A172,Sezoane!$C$6:$C$40,1)),A172&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A172,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A172,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H172" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H172" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A172,Sezoane!$C$6:$C$40,1)),A172&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A172,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A172,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I172" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I172" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A172,Sezoane!$C$6:$C$40,1)),A172&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A172,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A172,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15974,31 +16003,31 @@
       </c>
       <c r="C173" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A173,Sezoane!$C$6:$C$40,1)),A173&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A173,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A173,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D173" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D173" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A173,Sezoane!$C$6:$C$40,1)),A173&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A173,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A173,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E173" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E173" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A173,Sezoane!$C$6:$C$40,1)),A173&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A173,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A173,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F173" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F173" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A173,Sezoane!$C$6:$C$40,1)),A173&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A173,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A173,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G173" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G173" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A173,Sezoane!$C$6:$C$40,1)),A173&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A173,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A173,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H173" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H173" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A173,Sezoane!$C$6:$C$40,1)),A173&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A173,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A173,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I173" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I173" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A173,Sezoane!$C$6:$C$40,1)),A173&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A173,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A173,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16012,31 +16041,31 @@
       </c>
       <c r="C174" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A174,Sezoane!$C$6:$C$40,1)),A174&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A174,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A174,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D174" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D174" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A174,Sezoane!$C$6:$C$40,1)),A174&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A174,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A174,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E174" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E174" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A174,Sezoane!$C$6:$C$40,1)),A174&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A174,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A174,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F174" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F174" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A174,Sezoane!$C$6:$C$40,1)),A174&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A174,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A174,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G174" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G174" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A174,Sezoane!$C$6:$C$40,1)),A174&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A174,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A174,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H174" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H174" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A174,Sezoane!$C$6:$C$40,1)),A174&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A174,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A174,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I174" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I174" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A174,Sezoane!$C$6:$C$40,1)),A174&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A174,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A174,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16050,31 +16079,31 @@
       </c>
       <c r="C175" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A175,Sezoane!$C$6:$C$40,1)),A175&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A175,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A175,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D175" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D175" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A175,Sezoane!$C$6:$C$40,1)),A175&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A175,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A175,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E175" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E175" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A175,Sezoane!$C$6:$C$40,1)),A175&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A175,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A175,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F175" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F175" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A175,Sezoane!$C$6:$C$40,1)),A175&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A175,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A175,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G175" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G175" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A175,Sezoane!$C$6:$C$40,1)),A175&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A175,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A175,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H175" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H175" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A175,Sezoane!$C$6:$C$40,1)),A175&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A175,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A175,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I175" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I175" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A175,Sezoane!$C$6:$C$40,1)),A175&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A175,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A175,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16088,31 +16117,31 @@
       </c>
       <c r="C176" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A176,Sezoane!$C$6:$C$40,1)),A176&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A176,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A176,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D176" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D176" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A176,Sezoane!$C$6:$C$40,1)),A176&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A176,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A176,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E176" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E176" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A176,Sezoane!$C$6:$C$40,1)),A176&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A176,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A176,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F176" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F176" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A176,Sezoane!$C$6:$C$40,1)),A176&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A176,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A176,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G176" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G176" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A176,Sezoane!$C$6:$C$40,1)),A176&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A176,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A176,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H176" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H176" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A176,Sezoane!$C$6:$C$40,1)),A176&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A176,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A176,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I176" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I176" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A176,Sezoane!$C$6:$C$40,1)),A176&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A176,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A176,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16126,31 +16155,31 @@
       </c>
       <c r="C177" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A177,Sezoane!$C$6:$C$40,1)),A177&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A177,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A177,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D177" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D177" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A177,Sezoane!$C$6:$C$40,1)),A177&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A177,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A177,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E177" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E177" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A177,Sezoane!$C$6:$C$40,1)),A177&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A177,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A177,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F177" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F177" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A177,Sezoane!$C$6:$C$40,1)),A177&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A177,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A177,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G177" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G177" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A177,Sezoane!$C$6:$C$40,1)),A177&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A177,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A177,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H177" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H177" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A177,Sezoane!$C$6:$C$40,1)),A177&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A177,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A177,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I177" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I177" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A177,Sezoane!$C$6:$C$40,1)),A177&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A177,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A177,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16164,31 +16193,31 @@
       </c>
       <c r="C178" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A178,Sezoane!$C$6:$C$40,1)),A178&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A178,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A178,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D178" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D178" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A178,Sezoane!$C$6:$C$40,1)),A178&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A178,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A178,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E178" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E178" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A178,Sezoane!$C$6:$C$40,1)),A178&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A178,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A178,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F178" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F178" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A178,Sezoane!$C$6:$C$40,1)),A178&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A178,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A178,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G178" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G178" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A178,Sezoane!$C$6:$C$40,1)),A178&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A178,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A178,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H178" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H178" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A178,Sezoane!$C$6:$C$40,1)),A178&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A178,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A178,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I178" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I178" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A178,Sezoane!$C$6:$C$40,1)),A178&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A178,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A178,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16202,31 +16231,31 @@
       </c>
       <c r="C179" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A179,Sezoane!$C$6:$C$40,1)),A179&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A179,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A179,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D179" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D179" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A179,Sezoane!$C$6:$C$40,1)),A179&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A179,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A179,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E179" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E179" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A179,Sezoane!$C$6:$C$40,1)),A179&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A179,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A179,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F179" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F179" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A179,Sezoane!$C$6:$C$40,1)),A179&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A179,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A179,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G179" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G179" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A179,Sezoane!$C$6:$C$40,1)),A179&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A179,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A179,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H179" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H179" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A179,Sezoane!$C$6:$C$40,1)),A179&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A179,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A179,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I179" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I179" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A179,Sezoane!$C$6:$C$40,1)),A179&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A179,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A179,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16240,31 +16269,31 @@
       </c>
       <c r="C180" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A180,Sezoane!$C$6:$C$40,1)),A180&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A180,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A180,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D180" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D180" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A180,Sezoane!$C$6:$C$40,1)),A180&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A180,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A180,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E180" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E180" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A180,Sezoane!$C$6:$C$40,1)),A180&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A180,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A180,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F180" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F180" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A180,Sezoane!$C$6:$C$40,1)),A180&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A180,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A180,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G180" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G180" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A180,Sezoane!$C$6:$C$40,1)),A180&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A180,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A180,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H180" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H180" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A180,Sezoane!$C$6:$C$40,1)),A180&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A180,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A180,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I180" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I180" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A180,Sezoane!$C$6:$C$40,1)),A180&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A180,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A180,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16278,31 +16307,31 @@
       </c>
       <c r="C181" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A181,Sezoane!$C$6:$C$40,1)),A181&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A181,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A181,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D181" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D181" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A181,Sezoane!$C$6:$C$40,1)),A181&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A181,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A181,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E181" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E181" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A181,Sezoane!$C$6:$C$40,1)),A181&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A181,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A181,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F181" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F181" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A181,Sezoane!$C$6:$C$40,1)),A181&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A181,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A181,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G181" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G181" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A181,Sezoane!$C$6:$C$40,1)),A181&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A181,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A181,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H181" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H181" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A181,Sezoane!$C$6:$C$40,1)),A181&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A181,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A181,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I181" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I181" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A181,Sezoane!$C$6:$C$40,1)),A181&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A181,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A181,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16316,31 +16345,31 @@
       </c>
       <c r="C182" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A182,Sezoane!$C$6:$C$40,1)),A182&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A182,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A182,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D182" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D182" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A182,Sezoane!$C$6:$C$40,1)),A182&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A182,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A182,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E182" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E182" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A182,Sezoane!$C$6:$C$40,1)),A182&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A182,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A182,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F182" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F182" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A182,Sezoane!$C$6:$C$40,1)),A182&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A182,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A182,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G182" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G182" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A182,Sezoane!$C$6:$C$40,1)),A182&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A182,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A182,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H182" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H182" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A182,Sezoane!$C$6:$C$40,1)),A182&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A182,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A182,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I182" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I182" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A182,Sezoane!$C$6:$C$40,1)),A182&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A182,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A182,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16354,31 +16383,31 @@
       </c>
       <c r="C183" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A183,Sezoane!$C$6:$C$40,1)),A183&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A183,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A183,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D183" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D183" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A183,Sezoane!$C$6:$C$40,1)),A183&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A183,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A183,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E183" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E183" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A183,Sezoane!$C$6:$C$40,1)),A183&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A183,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A183,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F183" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F183" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A183,Sezoane!$C$6:$C$40,1)),A183&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A183,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A183,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G183" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G183" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A183,Sezoane!$C$6:$C$40,1)),A183&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A183,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A183,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H183" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H183" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A183,Sezoane!$C$6:$C$40,1)),A183&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A183,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A183,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I183" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I183" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A183,Sezoane!$C$6:$C$40,1)),A183&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A183,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A183,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16392,31 +16421,31 @@
       </c>
       <c r="C184" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A184,Sezoane!$C$6:$C$40,1)),A184&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A184,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A184,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D184" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D184" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A184,Sezoane!$C$6:$C$40,1)),A184&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A184,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A184,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E184" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E184" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A184,Sezoane!$C$6:$C$40,1)),A184&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A184,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A184,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F184" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F184" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A184,Sezoane!$C$6:$C$40,1)),A184&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A184,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A184,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G184" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G184" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A184,Sezoane!$C$6:$C$40,1)),A184&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A184,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A184,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H184" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H184" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A184,Sezoane!$C$6:$C$40,1)),A184&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A184,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A184,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I184" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I184" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A184,Sezoane!$C$6:$C$40,1)),A184&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A184,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A184,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16430,31 +16459,31 @@
       </c>
       <c r="C185" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A185,Sezoane!$C$6:$C$40,1)),A185&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A185,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A185,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D185" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D185" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A185,Sezoane!$C$6:$C$40,1)),A185&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A185,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A185,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E185" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E185" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A185,Sezoane!$C$6:$C$40,1)),A185&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A185,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A185,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F185" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F185" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A185,Sezoane!$C$6:$C$40,1)),A185&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A185,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A185,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G185" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G185" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A185,Sezoane!$C$6:$C$40,1)),A185&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A185,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A185,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H185" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H185" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A185,Sezoane!$C$6:$C$40,1)),A185&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A185,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A185,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I185" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I185" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A185,Sezoane!$C$6:$C$40,1)),A185&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A185,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A185,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16468,31 +16497,31 @@
       </c>
       <c r="C186" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A186,Sezoane!$C$6:$C$40,1)),A186&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A186,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A186,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D186" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D186" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A186,Sezoane!$C$6:$C$40,1)),A186&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A186,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A186,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E186" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E186" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A186,Sezoane!$C$6:$C$40,1)),A186&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A186,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A186,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F186" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F186" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A186,Sezoane!$C$6:$C$40,1)),A186&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A186,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A186,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G186" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G186" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A186,Sezoane!$C$6:$C$40,1)),A186&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A186,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A186,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H186" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H186" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A186,Sezoane!$C$6:$C$40,1)),A186&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A186,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A186,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I186" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I186" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A186,Sezoane!$C$6:$C$40,1)),A186&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A186,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A186,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16506,31 +16535,31 @@
       </c>
       <c r="C187" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A187,Sezoane!$C$6:$C$40,1)),A187&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A187,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A187,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D187" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D187" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A187,Sezoane!$C$6:$C$40,1)),A187&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A187,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A187,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E187" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E187" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A187,Sezoane!$C$6:$C$40,1)),A187&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A187,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A187,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F187" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F187" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A187,Sezoane!$C$6:$C$40,1)),A187&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A187,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A187,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G187" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G187" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A187,Sezoane!$C$6:$C$40,1)),A187&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A187,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A187,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H187" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H187" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A187,Sezoane!$C$6:$C$40,1)),A187&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A187,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A187,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I187" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I187" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A187,Sezoane!$C$6:$C$40,1)),A187&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A187,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A187,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16544,31 +16573,31 @@
       </c>
       <c r="C188" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A188,Sezoane!$C$6:$C$40,1)),A188&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A188,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A188,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D188" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D188" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A188,Sezoane!$C$6:$C$40,1)),A188&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A188,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A188,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E188" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E188" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A188,Sezoane!$C$6:$C$40,1)),A188&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A188,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A188,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F188" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F188" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A188,Sezoane!$C$6:$C$40,1)),A188&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A188,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A188,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G188" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G188" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A188,Sezoane!$C$6:$C$40,1)),A188&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A188,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A188,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H188" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H188" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A188,Sezoane!$C$6:$C$40,1)),A188&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A188,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A188,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I188" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I188" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A188,Sezoane!$C$6:$C$40,1)),A188&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A188,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A188,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16582,31 +16611,31 @@
       </c>
       <c r="C189" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A189,Sezoane!$C$6:$C$40,1)),A189&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A189,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A189,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D189" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D189" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A189,Sezoane!$C$6:$C$40,1)),A189&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A189,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A189,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E189" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E189" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A189,Sezoane!$C$6:$C$40,1)),A189&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A189,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A189,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F189" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F189" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A189,Sezoane!$C$6:$C$40,1)),A189&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A189,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A189,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G189" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G189" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A189,Sezoane!$C$6:$C$40,1)),A189&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A189,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A189,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H189" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H189" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A189,Sezoane!$C$6:$C$40,1)),A189&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A189,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A189,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I189" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I189" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A189,Sezoane!$C$6:$C$40,1)),A189&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A189,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A189,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16620,31 +16649,31 @@
       </c>
       <c r="C190" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A190,Sezoane!$C$6:$C$40,1)),A190&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A190,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A190,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D190" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D190" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A190,Sezoane!$C$6:$C$40,1)),A190&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A190,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A190,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E190" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E190" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A190,Sezoane!$C$6:$C$40,1)),A190&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A190,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A190,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F190" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F190" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A190,Sezoane!$C$6:$C$40,1)),A190&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A190,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A190,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G190" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G190" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A190,Sezoane!$C$6:$C$40,1)),A190&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A190,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A190,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H190" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H190" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A190,Sezoane!$C$6:$C$40,1)),A190&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A190,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A190,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I190" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I190" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A190,Sezoane!$C$6:$C$40,1)),A190&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A190,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A190,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16658,31 +16687,31 @@
       </c>
       <c r="C191" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A191,Sezoane!$C$6:$C$40,1)),A191&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A191,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A191,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D191" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D191" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A191,Sezoane!$C$6:$C$40,1)),A191&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A191,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A191,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E191" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E191" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A191,Sezoane!$C$6:$C$40,1)),A191&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A191,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A191,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F191" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F191" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A191,Sezoane!$C$6:$C$40,1)),A191&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A191,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A191,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G191" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G191" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A191,Sezoane!$C$6:$C$40,1)),A191&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A191,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A191,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H191" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H191" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A191,Sezoane!$C$6:$C$40,1)),A191&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A191,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A191,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I191" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I191" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A191,Sezoane!$C$6:$C$40,1)),A191&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A191,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A191,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16696,31 +16725,31 @@
       </c>
       <c r="C192" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A192,Sezoane!$C$6:$C$40,1)),A192&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A192,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A192,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D192" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D192" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A192,Sezoane!$C$6:$C$40,1)),A192&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A192,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A192,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E192" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E192" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A192,Sezoane!$C$6:$C$40,1)),A192&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A192,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A192,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F192" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F192" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A192,Sezoane!$C$6:$C$40,1)),A192&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A192,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A192,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G192" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G192" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A192,Sezoane!$C$6:$C$40,1)),A192&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A192,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A192,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H192" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H192" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A192,Sezoane!$C$6:$C$40,1)),A192&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A192,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A192,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I192" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I192" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A192,Sezoane!$C$6:$C$40,1)),A192&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A192,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A192,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16734,31 +16763,31 @@
       </c>
       <c r="C193" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A193,Sezoane!$C$6:$C$40,1)),A193&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A193,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A193,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D193" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D193" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A193,Sezoane!$C$6:$C$40,1)),A193&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A193,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A193,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E193" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E193" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A193,Sezoane!$C$6:$C$40,1)),A193&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A193,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A193,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F193" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F193" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A193,Sezoane!$C$6:$C$40,1)),A193&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A193,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A193,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G193" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G193" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A193,Sezoane!$C$6:$C$40,1)),A193&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A193,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A193,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H193" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H193" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A193,Sezoane!$C$6:$C$40,1)),A193&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A193,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A193,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I193" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I193" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A193,Sezoane!$C$6:$C$40,1)),A193&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A193,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A193,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16772,31 +16801,31 @@
       </c>
       <c r="C194" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A194,Sezoane!$C$6:$C$40,1)),A194&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A194,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A194,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D194" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D194" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A194,Sezoane!$C$6:$C$40,1)),A194&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A194,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A194,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E194" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E194" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A194,Sezoane!$C$6:$C$40,1)),A194&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A194,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A194,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F194" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F194" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A194,Sezoane!$C$6:$C$40,1)),A194&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A194,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A194,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G194" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G194" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A194,Sezoane!$C$6:$C$40,1)),A194&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A194,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A194,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H194" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H194" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A194,Sezoane!$C$6:$C$40,1)),A194&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A194,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A194,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I194" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I194" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A194,Sezoane!$C$6:$C$40,1)),A194&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A194,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A194,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16810,31 +16839,31 @@
       </c>
       <c r="C195" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A195,Sezoane!$C$6:$C$40,1)),A195&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A195,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A195,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D195" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D195" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A195,Sezoane!$C$6:$C$40,1)),A195&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A195,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A195,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E195" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E195" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A195,Sezoane!$C$6:$C$40,1)),A195&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A195,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A195,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F195" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F195" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A195,Sezoane!$C$6:$C$40,1)),A195&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A195,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A195,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G195" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G195" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A195,Sezoane!$C$6:$C$40,1)),A195&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A195,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A195,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H195" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H195" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A195,Sezoane!$C$6:$C$40,1)),A195&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A195,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A195,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I195" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I195" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A195,Sezoane!$C$6:$C$40,1)),A195&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A195,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A195,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16848,31 +16877,31 @@
       </c>
       <c r="C196" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A196,Sezoane!$C$6:$C$40,1)),A196&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A196,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A196,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D196" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D196" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A196,Sezoane!$C$6:$C$40,1)),A196&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A196,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A196,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E196" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E196" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A196,Sezoane!$C$6:$C$40,1)),A196&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A196,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A196,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F196" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F196" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A196,Sezoane!$C$6:$C$40,1)),A196&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A196,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A196,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G196" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G196" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A196,Sezoane!$C$6:$C$40,1)),A196&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A196,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A196,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H196" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H196" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A196,Sezoane!$C$6:$C$40,1)),A196&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A196,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A196,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I196" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I196" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A196,Sezoane!$C$6:$C$40,1)),A196&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A196,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A196,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16886,31 +16915,31 @@
       </c>
       <c r="C197" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A197,Sezoane!$C$6:$C$40,1)),A197&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A197,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A197,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D197" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D197" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A197,Sezoane!$C$6:$C$40,1)),A197&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A197,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A197,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E197" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E197" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A197,Sezoane!$C$6:$C$40,1)),A197&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A197,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A197,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F197" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F197" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A197,Sezoane!$C$6:$C$40,1)),A197&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A197,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A197,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G197" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G197" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A197,Sezoane!$C$6:$C$40,1)),A197&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A197,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A197,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H197" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H197" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A197,Sezoane!$C$6:$C$40,1)),A197&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A197,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A197,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I197" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I197" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A197,Sezoane!$C$6:$C$40,1)),A197&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A197,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A197,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16924,31 +16953,31 @@
       </c>
       <c r="C198" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A198,Sezoane!$C$6:$C$40,1)),A198&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A198,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A198,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D198" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D198" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A198,Sezoane!$C$6:$C$40,1)),A198&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A198,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A198,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E198" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E198" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A198,Sezoane!$C$6:$C$40,1)),A198&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A198,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A198,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F198" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F198" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A198,Sezoane!$C$6:$C$40,1)),A198&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A198,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A198,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G198" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G198" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A198,Sezoane!$C$6:$C$40,1)),A198&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A198,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A198,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H198" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H198" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A198,Sezoane!$C$6:$C$40,1)),A198&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A198,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A198,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I198" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I198" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A198,Sezoane!$C$6:$C$40,1)),A198&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A198,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A198,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16962,31 +16991,31 @@
       </c>
       <c r="C199" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A199,Sezoane!$C$6:$C$40,1)),A199&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A199,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A199,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D199" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D199" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A199,Sezoane!$C$6:$C$40,1)),A199&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A199,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A199,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E199" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E199" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A199,Sezoane!$C$6:$C$40,1)),A199&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A199,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A199,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F199" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F199" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A199,Sezoane!$C$6:$C$40,1)),A199&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A199,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A199,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G199" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G199" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A199,Sezoane!$C$6:$C$40,1)),A199&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A199,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A199,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H199" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H199" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A199,Sezoane!$C$6:$C$40,1)),A199&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A199,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A199,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I199" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I199" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A199,Sezoane!$C$6:$C$40,1)),A199&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A199,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A199,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17000,31 +17029,31 @@
       </c>
       <c r="C200" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A200,Sezoane!$C$6:$C$40,1)),A200&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A200,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A200,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D200" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D200" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A200,Sezoane!$C$6:$C$40,1)),A200&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A200,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A200,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E200" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E200" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A200,Sezoane!$C$6:$C$40,1)),A200&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A200,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A200,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F200" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F200" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A200,Sezoane!$C$6:$C$40,1)),A200&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A200,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A200,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G200" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G200" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A200,Sezoane!$C$6:$C$40,1)),A200&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A200,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A200,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H200" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H200" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A200,Sezoane!$C$6:$C$40,1)),A200&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A200,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A200,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I200" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I200" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A200,Sezoane!$C$6:$C$40,1)),A200&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A200,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A200,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17038,31 +17067,31 @@
       </c>
       <c r="C201" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A201,Sezoane!$C$6:$C$40,1)),A201&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A201,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A201,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D201" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D201" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A201,Sezoane!$C$6:$C$40,1)),A201&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A201,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A201,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E201" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E201" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A201,Sezoane!$C$6:$C$40,1)),A201&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A201,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A201,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F201" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F201" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A201,Sezoane!$C$6:$C$40,1)),A201&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A201,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A201,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G201" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G201" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A201,Sezoane!$C$6:$C$40,1)),A201&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A201,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A201,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H201" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H201" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A201,Sezoane!$C$6:$C$40,1)),A201&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A201,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A201,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I201" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I201" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A201,Sezoane!$C$6:$C$40,1)),A201&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A201,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A201,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17076,31 +17105,31 @@
       </c>
       <c r="C202" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A202,Sezoane!$C$6:$C$40,1)),A202&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A202,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A202,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D202" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D202" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A202,Sezoane!$C$6:$C$40,1)),A202&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A202,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A202,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E202" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E202" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A202,Sezoane!$C$6:$C$40,1)),A202&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A202,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A202,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F202" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F202" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A202,Sezoane!$C$6:$C$40,1)),A202&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A202,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A202,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G202" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G202" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A202,Sezoane!$C$6:$C$40,1)),A202&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A202,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A202,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H202" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H202" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A202,Sezoane!$C$6:$C$40,1)),A202&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A202,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A202,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I202" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I202" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A202,Sezoane!$C$6:$C$40,1)),A202&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A202,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A202,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17114,31 +17143,31 @@
       </c>
       <c r="C203" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A203,Sezoane!$C$6:$C$40,1)),A203&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A203,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A203,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D203" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D203" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A203,Sezoane!$C$6:$C$40,1)),A203&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A203,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A203,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E203" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E203" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A203,Sezoane!$C$6:$C$40,1)),A203&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A203,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A203,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F203" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F203" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A203,Sezoane!$C$6:$C$40,1)),A203&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A203,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A203,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G203" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G203" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A203,Sezoane!$C$6:$C$40,1)),A203&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A203,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A203,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H203" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H203" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A203,Sezoane!$C$6:$C$40,1)),A203&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A203,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A203,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I203" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I203" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A203,Sezoane!$C$6:$C$40,1)),A203&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A203,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A203,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17152,31 +17181,31 @@
       </c>
       <c r="C204" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A204,Sezoane!$C$6:$C$40,1)),A204&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A204,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A204,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D204" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D204" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A204,Sezoane!$C$6:$C$40,1)),A204&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A204,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A204,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E204" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E204" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A204,Sezoane!$C$6:$C$40,1)),A204&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A204,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A204,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F204" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F204" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A204,Sezoane!$C$6:$C$40,1)),A204&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A204,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A204,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G204" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G204" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A204,Sezoane!$C$6:$C$40,1)),A204&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A204,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A204,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H204" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H204" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A204,Sezoane!$C$6:$C$40,1)),A204&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A204,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A204,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I204" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I204" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A204,Sezoane!$C$6:$C$40,1)),A204&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A204,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A204,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17190,31 +17219,31 @@
       </c>
       <c r="C205" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A205,Sezoane!$C$6:$C$40,1)),A205&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A205,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A205,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D205" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D205" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A205,Sezoane!$C$6:$C$40,1)),A205&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A205,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A205,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E205" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E205" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A205,Sezoane!$C$6:$C$40,1)),A205&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A205,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A205,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F205" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F205" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A205,Sezoane!$C$6:$C$40,1)),A205&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A205,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A205,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G205" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G205" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A205,Sezoane!$C$6:$C$40,1)),A205&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A205,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A205,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H205" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H205" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A205,Sezoane!$C$6:$C$40,1)),A205&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A205,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A205,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I205" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I205" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A205,Sezoane!$C$6:$C$40,1)),A205&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A205,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A205,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17228,31 +17257,31 @@
       </c>
       <c r="C206" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A206,Sezoane!$C$6:$C$40,1)),A206&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A206,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A206,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D206" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D206" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A206,Sezoane!$C$6:$C$40,1)),A206&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A206,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A206,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E206" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E206" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A206,Sezoane!$C$6:$C$40,1)),A206&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A206,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A206,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F206" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F206" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A206,Sezoane!$C$6:$C$40,1)),A206&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A206,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A206,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G206" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G206" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A206,Sezoane!$C$6:$C$40,1)),A206&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A206,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A206,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H206" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H206" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A206,Sezoane!$C$6:$C$40,1)),A206&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A206,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A206,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I206" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I206" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A206,Sezoane!$C$6:$C$40,1)),A206&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A206,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A206,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17266,31 +17295,31 @@
       </c>
       <c r="C207" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A207,Sezoane!$C$6:$C$40,1)),A207&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A207,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A207,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D207" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D207" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A207,Sezoane!$C$6:$C$40,1)),A207&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A207,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A207,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E207" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E207" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A207,Sezoane!$C$6:$C$40,1)),A207&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A207,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A207,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F207" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F207" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A207,Sezoane!$C$6:$C$40,1)),A207&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A207,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A207,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G207" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G207" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A207,Sezoane!$C$6:$C$40,1)),A207&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A207,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A207,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H207" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H207" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A207,Sezoane!$C$6:$C$40,1)),A207&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A207,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A207,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I207" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I207" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A207,Sezoane!$C$6:$C$40,1)),A207&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A207,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A207,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17304,31 +17333,31 @@
       </c>
       <c r="C208" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A208,Sezoane!$C$6:$C$40,1)),A208&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A208,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A208,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D208" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D208" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A208,Sezoane!$C$6:$C$40,1)),A208&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A208,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A208,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E208" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E208" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A208,Sezoane!$C$6:$C$40,1)),A208&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A208,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A208,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F208" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F208" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A208,Sezoane!$C$6:$C$40,1)),A208&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A208,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A208,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G208" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G208" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A208,Sezoane!$C$6:$C$40,1)),A208&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A208,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A208,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H208" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H208" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A208,Sezoane!$C$6:$C$40,1)),A208&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A208,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A208,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I208" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I208" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A208,Sezoane!$C$6:$C$40,1)),A208&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A208,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A208,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17342,31 +17371,31 @@
       </c>
       <c r="C209" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A209,Sezoane!$C$6:$C$40,1)),A209&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A209,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A209,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D209" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D209" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A209,Sezoane!$C$6:$C$40,1)),A209&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A209,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A209,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E209" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E209" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A209,Sezoane!$C$6:$C$40,1)),A209&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A209,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A209,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F209" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F209" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A209,Sezoane!$C$6:$C$40,1)),A209&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A209,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A209,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G209" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G209" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A209,Sezoane!$C$6:$C$40,1)),A209&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A209,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A209,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H209" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H209" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A209,Sezoane!$C$6:$C$40,1)),A209&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A209,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A209,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I209" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I209" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A209,Sezoane!$C$6:$C$40,1)),A209&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A209,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A209,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17380,31 +17409,31 @@
       </c>
       <c r="C210" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A210,Sezoane!$C$6:$C$40,1)),A210&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A210,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A210,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D210" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D210" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A210,Sezoane!$C$6:$C$40,1)),A210&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A210,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A210,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E210" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E210" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A210,Sezoane!$C$6:$C$40,1)),A210&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A210,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A210,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F210" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F210" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A210,Sezoane!$C$6:$C$40,1)),A210&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A210,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A210,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G210" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G210" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A210,Sezoane!$C$6:$C$40,1)),A210&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A210,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A210,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H210" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H210" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A210,Sezoane!$C$6:$C$40,1)),A210&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A210,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A210,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I210" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I210" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A210,Sezoane!$C$6:$C$40,1)),A210&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A210,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A210,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17418,31 +17447,31 @@
       </c>
       <c r="C211" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A211,Sezoane!$C$6:$C$40,1)),A211&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A211,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A211,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D211" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D211" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A211,Sezoane!$C$6:$C$40,1)),A211&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A211,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A211,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E211" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E211" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A211,Sezoane!$C$6:$C$40,1)),A211&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A211,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A211,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F211" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F211" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A211,Sezoane!$C$6:$C$40,1)),A211&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A211,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A211,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G211" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G211" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A211,Sezoane!$C$6:$C$40,1)),A211&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A211,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A211,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H211" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H211" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A211,Sezoane!$C$6:$C$40,1)),A211&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A211,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A211,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I211" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I211" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A211,Sezoane!$C$6:$C$40,1)),A211&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A211,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A211,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17456,31 +17485,31 @@
       </c>
       <c r="C212" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A212,Sezoane!$C$6:$C$40,1)),A212&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A212,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A212,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D212" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D212" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A212,Sezoane!$C$6:$C$40,1)),A212&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A212,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A212,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E212" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E212" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A212,Sezoane!$C$6:$C$40,1)),A212&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A212,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A212,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F212" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F212" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A212,Sezoane!$C$6:$C$40,1)),A212&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A212,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A212,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G212" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G212" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A212,Sezoane!$C$6:$C$40,1)),A212&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A212,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A212,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H212" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H212" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A212,Sezoane!$C$6:$C$40,1)),A212&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A212,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A212,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I212" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I212" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A212,Sezoane!$C$6:$C$40,1)),A212&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A212,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A212,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17494,31 +17523,31 @@
       </c>
       <c r="C213" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A213,Sezoane!$C$6:$C$40,1)),A213&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A213,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A213,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D213" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D213" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A213,Sezoane!$C$6:$C$40,1)),A213&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A213,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A213,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E213" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E213" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A213,Sezoane!$C$6:$C$40,1)),A213&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A213,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A213,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F213" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F213" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A213,Sezoane!$C$6:$C$40,1)),A213&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A213,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A213,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G213" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G213" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A213,Sezoane!$C$6:$C$40,1)),A213&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A213,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A213,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H213" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H213" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A213,Sezoane!$C$6:$C$40,1)),A213&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A213,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A213,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I213" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I213" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A213,Sezoane!$C$6:$C$40,1)),A213&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A213,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A213,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17532,31 +17561,31 @@
       </c>
       <c r="C214" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A214,Sezoane!$C$6:$C$40,1)),A214&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A214,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A214,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D214" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D214" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A214,Sezoane!$C$6:$C$40,1)),A214&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A214,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A214,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E214" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E214" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A214,Sezoane!$C$6:$C$40,1)),A214&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A214,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A214,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F214" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F214" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A214,Sezoane!$C$6:$C$40,1)),A214&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A214,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A214,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G214" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G214" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A214,Sezoane!$C$6:$C$40,1)),A214&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A214,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A214,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H214" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H214" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A214,Sezoane!$C$6:$C$40,1)),A214&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A214,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A214,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I214" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I214" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A214,Sezoane!$C$6:$C$40,1)),A214&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A214,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A214,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17570,31 +17599,31 @@
       </c>
       <c r="C215" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A215,Sezoane!$C$6:$C$40,1)),A215&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A215,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A215,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D215" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D215" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A215,Sezoane!$C$6:$C$40,1)),A215&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A215,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A215,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E215" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E215" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A215,Sezoane!$C$6:$C$40,1)),A215&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A215,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A215,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F215" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F215" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A215,Sezoane!$C$6:$C$40,1)),A215&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A215,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A215,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G215" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G215" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A215,Sezoane!$C$6:$C$40,1)),A215&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A215,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A215,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H215" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H215" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A215,Sezoane!$C$6:$C$40,1)),A215&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A215,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A215,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I215" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I215" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A215,Sezoane!$C$6:$C$40,1)),A215&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A215,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A215,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17608,31 +17637,31 @@
       </c>
       <c r="C216" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A216,Sezoane!$C$6:$C$40,1)),A216&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A216,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A216,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D216" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D216" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A216,Sezoane!$C$6:$C$40,1)),A216&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A216,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A216,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E216" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E216" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A216,Sezoane!$C$6:$C$40,1)),A216&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A216,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A216,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F216" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F216" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A216,Sezoane!$C$6:$C$40,1)),A216&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A216,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A216,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G216" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G216" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A216,Sezoane!$C$6:$C$40,1)),A216&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A216,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A216,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H216" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H216" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A216,Sezoane!$C$6:$C$40,1)),A216&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A216,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A216,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I216" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I216" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A216,Sezoane!$C$6:$C$40,1)),A216&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A216,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A216,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17646,31 +17675,31 @@
       </c>
       <c r="C217" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A217,Sezoane!$C$6:$C$40,1)),A217&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A217,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A217,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D217" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D217" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A217,Sezoane!$C$6:$C$40,1)),A217&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A217,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A217,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E217" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E217" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A217,Sezoane!$C$6:$C$40,1)),A217&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A217,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A217,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F217" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F217" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A217,Sezoane!$C$6:$C$40,1)),A217&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A217,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A217,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G217" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G217" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A217,Sezoane!$C$6:$C$40,1)),A217&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A217,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A217,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H217" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H217" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A217,Sezoane!$C$6:$C$40,1)),A217&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A217,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A217,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I217" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I217" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A217,Sezoane!$C$6:$C$40,1)),A217&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A217,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A217,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17684,31 +17713,31 @@
       </c>
       <c r="C218" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A218,Sezoane!$C$6:$C$40,1)),A218&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A218,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A218,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D218" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D218" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A218,Sezoane!$C$6:$C$40,1)),A218&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A218,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A218,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E218" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E218" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A218,Sezoane!$C$6:$C$40,1)),A218&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A218,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A218,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F218" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F218" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A218,Sezoane!$C$6:$C$40,1)),A218&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A218,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A218,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G218" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G218" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A218,Sezoane!$C$6:$C$40,1)),A218&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A218,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A218,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H218" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H218" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A218,Sezoane!$C$6:$C$40,1)),A218&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A218,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A218,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I218" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I218" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A218,Sezoane!$C$6:$C$40,1)),A218&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A218,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A218,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17722,31 +17751,31 @@
       </c>
       <c r="C219" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A219,Sezoane!$C$6:$C$40,1)),A219&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A219,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A219,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D219" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D219" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A219,Sezoane!$C$6:$C$40,1)),A219&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A219,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A219,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E219" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E219" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A219,Sezoane!$C$6:$C$40,1)),A219&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A219,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A219,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F219" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F219" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A219,Sezoane!$C$6:$C$40,1)),A219&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A219,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A219,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G219" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G219" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A219,Sezoane!$C$6:$C$40,1)),A219&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A219,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A219,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H219" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H219" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A219,Sezoane!$C$6:$C$40,1)),A219&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A219,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A219,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I219" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I219" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A219,Sezoane!$C$6:$C$40,1)),A219&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A219,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A219,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17760,31 +17789,31 @@
       </c>
       <c r="C220" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A220,Sezoane!$C$6:$C$40,1)),A220&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A220,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A220,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D220" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D220" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A220,Sezoane!$C$6:$C$40,1)),A220&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A220,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A220,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E220" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E220" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A220,Sezoane!$C$6:$C$40,1)),A220&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A220,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A220,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F220" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F220" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A220,Sezoane!$C$6:$C$40,1)),A220&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A220,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A220,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G220" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G220" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A220,Sezoane!$C$6:$C$40,1)),A220&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A220,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A220,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H220" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H220" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A220,Sezoane!$C$6:$C$40,1)),A220&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A220,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A220,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I220" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I220" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A220,Sezoane!$C$6:$C$40,1)),A220&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A220,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A220,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17798,31 +17827,31 @@
       </c>
       <c r="C221" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A221,Sezoane!$C$6:$C$40,1)),A221&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A221,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A221,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D221" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D221" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A221,Sezoane!$C$6:$C$40,1)),A221&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A221,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A221,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E221" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E221" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A221,Sezoane!$C$6:$C$40,1)),A221&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A221,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A221,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F221" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F221" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A221,Sezoane!$C$6:$C$40,1)),A221&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A221,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A221,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G221" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G221" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A221,Sezoane!$C$6:$C$40,1)),A221&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A221,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A221,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H221" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H221" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A221,Sezoane!$C$6:$C$40,1)),A221&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A221,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A221,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I221" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I221" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A221,Sezoane!$C$6:$C$40,1)),A221&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A221,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A221,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17836,31 +17865,31 @@
       </c>
       <c r="C222" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A222,Sezoane!$C$6:$C$40,1)),A222&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A222,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A222,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D222" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D222" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A222,Sezoane!$C$6:$C$40,1)),A222&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A222,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A222,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E222" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E222" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A222,Sezoane!$C$6:$C$40,1)),A222&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A222,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A222,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F222" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F222" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A222,Sezoane!$C$6:$C$40,1)),A222&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A222,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A222,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G222" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G222" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A222,Sezoane!$C$6:$C$40,1)),A222&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A222,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A222,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H222" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H222" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A222,Sezoane!$C$6:$C$40,1)),A222&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A222,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A222,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I222" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I222" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A222,Sezoane!$C$6:$C$40,1)),A222&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A222,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A222,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17874,31 +17903,31 @@
       </c>
       <c r="C223" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A223,Sezoane!$C$6:$C$40,1)),A223&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A223,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A223,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D223" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D223" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A223,Sezoane!$C$6:$C$40,1)),A223&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A223,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A223,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E223" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E223" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A223,Sezoane!$C$6:$C$40,1)),A223&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A223,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A223,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F223" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F223" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A223,Sezoane!$C$6:$C$40,1)),A223&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A223,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A223,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G223" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G223" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A223,Sezoane!$C$6:$C$40,1)),A223&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A223,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A223,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H223" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H223" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A223,Sezoane!$C$6:$C$40,1)),A223&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A223,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A223,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I223" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I223" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A223,Sezoane!$C$6:$C$40,1)),A223&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A223,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A223,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17912,31 +17941,31 @@
       </c>
       <c r="C224" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A224,Sezoane!$C$6:$C$40,1)),A224&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A224,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A224,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D224" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D224" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A224,Sezoane!$C$6:$C$40,1)),A224&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A224,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A224,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E224" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E224" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A224,Sezoane!$C$6:$C$40,1)),A224&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A224,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A224,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F224" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F224" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A224,Sezoane!$C$6:$C$40,1)),A224&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A224,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A224,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G224" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G224" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A224,Sezoane!$C$6:$C$40,1)),A224&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A224,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A224,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H224" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H224" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A224,Sezoane!$C$6:$C$40,1)),A224&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A224,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A224,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I224" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I224" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A224,Sezoane!$C$6:$C$40,1)),A224&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A224,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A224,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17950,31 +17979,31 @@
       </c>
       <c r="C225" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A225,Sezoane!$C$6:$C$40,1)),A225&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A225,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A225,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D225" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D225" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A225,Sezoane!$C$6:$C$40,1)),A225&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A225,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A225,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E225" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E225" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A225,Sezoane!$C$6:$C$40,1)),A225&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A225,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A225,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F225" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F225" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A225,Sezoane!$C$6:$C$40,1)),A225&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A225,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A225,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G225" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G225" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A225,Sezoane!$C$6:$C$40,1)),A225&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A225,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A225,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H225" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H225" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A225,Sezoane!$C$6:$C$40,1)),A225&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A225,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A225,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I225" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I225" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A225,Sezoane!$C$6:$C$40,1)),A225&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A225,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A225,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17988,31 +18017,31 @@
       </c>
       <c r="C226" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A226,Sezoane!$C$6:$C$40,1)),A226&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A226,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A226,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D226" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D226" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A226,Sezoane!$C$6:$C$40,1)),A226&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A226,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A226,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E226" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E226" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A226,Sezoane!$C$6:$C$40,1)),A226&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A226,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A226,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F226" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F226" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A226,Sezoane!$C$6:$C$40,1)),A226&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A226,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A226,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G226" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G226" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A226,Sezoane!$C$6:$C$40,1)),A226&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A226,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A226,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H226" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H226" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A226,Sezoane!$C$6:$C$40,1)),A226&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A226,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A226,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I226" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I226" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A226,Sezoane!$C$6:$C$40,1)),A226&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A226,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A226,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18026,31 +18055,31 @@
       </c>
       <c r="C227" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A227,Sezoane!$C$6:$C$40,1)),A227&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A227,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A227,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D227" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D227" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A227,Sezoane!$C$6:$C$40,1)),A227&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A227,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A227,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E227" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E227" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A227,Sezoane!$C$6:$C$40,1)),A227&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A227,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A227,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F227" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F227" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A227,Sezoane!$C$6:$C$40,1)),A227&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A227,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A227,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G227" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G227" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A227,Sezoane!$C$6:$C$40,1)),A227&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A227,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A227,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H227" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H227" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A227,Sezoane!$C$6:$C$40,1)),A227&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A227,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A227,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I227" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I227" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A227,Sezoane!$C$6:$C$40,1)),A227&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A227,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A227,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18064,31 +18093,31 @@
       </c>
       <c r="C228" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A228,Sezoane!$C$6:$C$40,1)),A228&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A228,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A228,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D228" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D228" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A228,Sezoane!$C$6:$C$40,1)),A228&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A228,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A228,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E228" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E228" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A228,Sezoane!$C$6:$C$40,1)),A228&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A228,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A228,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F228" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F228" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A228,Sezoane!$C$6:$C$40,1)),A228&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A228,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A228,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G228" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G228" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A228,Sezoane!$C$6:$C$40,1)),A228&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A228,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A228,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H228" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H228" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A228,Sezoane!$C$6:$C$40,1)),A228&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A228,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A228,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I228" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I228" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A228,Sezoane!$C$6:$C$40,1)),A228&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A228,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A228,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18102,31 +18131,31 @@
       </c>
       <c r="C229" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A229,Sezoane!$C$6:$C$40,1)),A229&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A229,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A229,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D229" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D229" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A229,Sezoane!$C$6:$C$40,1)),A229&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A229,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A229,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E229" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E229" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A229,Sezoane!$C$6:$C$40,1)),A229&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A229,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A229,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F229" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F229" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A229,Sezoane!$C$6:$C$40,1)),A229&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A229,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A229,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G229" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G229" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A229,Sezoane!$C$6:$C$40,1)),A229&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A229,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A229,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H229" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H229" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A229,Sezoane!$C$6:$C$40,1)),A229&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A229,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A229,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I229" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I229" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A229,Sezoane!$C$6:$C$40,1)),A229&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A229,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A229,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18140,31 +18169,31 @@
       </c>
       <c r="C230" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A230,Sezoane!$C$6:$C$40,1)),A230&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A230,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A230,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D230" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D230" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A230,Sezoane!$C$6:$C$40,1)),A230&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A230,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A230,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E230" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E230" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A230,Sezoane!$C$6:$C$40,1)),A230&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A230,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A230,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F230" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F230" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A230,Sezoane!$C$6:$C$40,1)),A230&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A230,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A230,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G230" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G230" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A230,Sezoane!$C$6:$C$40,1)),A230&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A230,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A230,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H230" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H230" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A230,Sezoane!$C$6:$C$40,1)),A230&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A230,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A230,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I230" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I230" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A230,Sezoane!$C$6:$C$40,1)),A230&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A230,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A230,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18178,31 +18207,31 @@
       </c>
       <c r="C231" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A231,Sezoane!$C$6:$C$40,1)),A231&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A231,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A231,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D231" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D231" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A231,Sezoane!$C$6:$C$40,1)),A231&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A231,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A231,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E231" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E231" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A231,Sezoane!$C$6:$C$40,1)),A231&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A231,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A231,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F231" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F231" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A231,Sezoane!$C$6:$C$40,1)),A231&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A231,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A231,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G231" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G231" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A231,Sezoane!$C$6:$C$40,1)),A231&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A231,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A231,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H231" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H231" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A231,Sezoane!$C$6:$C$40,1)),A231&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A231,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A231,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I231" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I231" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A231,Sezoane!$C$6:$C$40,1)),A231&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A231,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A231,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18216,31 +18245,31 @@
       </c>
       <c r="C232" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A232,Sezoane!$C$6:$C$40,1)),A232&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A232,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A232,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D232" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D232" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A232,Sezoane!$C$6:$C$40,1)),A232&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A232,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A232,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E232" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E232" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A232,Sezoane!$C$6:$C$40,1)),A232&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A232,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A232,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F232" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F232" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A232,Sezoane!$C$6:$C$40,1)),A232&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A232,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A232,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G232" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G232" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A232,Sezoane!$C$6:$C$40,1)),A232&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A232,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A232,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H232" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H232" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A232,Sezoane!$C$6:$C$40,1)),A232&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A232,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A232,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I232" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I232" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A232,Sezoane!$C$6:$C$40,1)),A232&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A232,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A232,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18254,31 +18283,31 @@
       </c>
       <c r="C233" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A233,Sezoane!$C$6:$C$40,1)),A233&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A233,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A233,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D233" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D233" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A233,Sezoane!$C$6:$C$40,1)),A233&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A233,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A233,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E233" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E233" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A233,Sezoane!$C$6:$C$40,1)),A233&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A233,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A233,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F233" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F233" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A233,Sezoane!$C$6:$C$40,1)),A233&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A233,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A233,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G233" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G233" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A233,Sezoane!$C$6:$C$40,1)),A233&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A233,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A233,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H233" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H233" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A233,Sezoane!$C$6:$C$40,1)),A233&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A233,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A233,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I233" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I233" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A233,Sezoane!$C$6:$C$40,1)),A233&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A233,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A233,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18292,31 +18321,31 @@
       </c>
       <c r="C234" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A234,Sezoane!$C$6:$C$40,1)),A234&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A234,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A234,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D234" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D234" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A234,Sezoane!$C$6:$C$40,1)),A234&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A234,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A234,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E234" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E234" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A234,Sezoane!$C$6:$C$40,1)),A234&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A234,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A234,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F234" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F234" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A234,Sezoane!$C$6:$C$40,1)),A234&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A234,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A234,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G234" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G234" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A234,Sezoane!$C$6:$C$40,1)),A234&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A234,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A234,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H234" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H234" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A234,Sezoane!$C$6:$C$40,1)),A234&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A234,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A234,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I234" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I234" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A234,Sezoane!$C$6:$C$40,1)),A234&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A234,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A234,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18330,31 +18359,31 @@
       </c>
       <c r="C235" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A235,Sezoane!$C$6:$C$40,1)),A235&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A235,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A235,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D235" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D235" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A235,Sezoane!$C$6:$C$40,1)),A235&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A235,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A235,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E235" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E235" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A235,Sezoane!$C$6:$C$40,1)),A235&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A235,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A235,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F235" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F235" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A235,Sezoane!$C$6:$C$40,1)),A235&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A235,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A235,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G235" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G235" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A235,Sezoane!$C$6:$C$40,1)),A235&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A235,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A235,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H235" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H235" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A235,Sezoane!$C$6:$C$40,1)),A235&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A235,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A235,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I235" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I235" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A235,Sezoane!$C$6:$C$40,1)),A235&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A235,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A235,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18368,31 +18397,31 @@
       </c>
       <c r="C236" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A236,Sezoane!$C$6:$C$40,1)),A236&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A236,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A236,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D236" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D236" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A236,Sezoane!$C$6:$C$40,1)),A236&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A236,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A236,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E236" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E236" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A236,Sezoane!$C$6:$C$40,1)),A236&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A236,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A236,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F236" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F236" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A236,Sezoane!$C$6:$C$40,1)),A236&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A236,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A236,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G236" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G236" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A236,Sezoane!$C$6:$C$40,1)),A236&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A236,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A236,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H236" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H236" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A236,Sezoane!$C$6:$C$40,1)),A236&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A236,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A236,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I236" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I236" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A236,Sezoane!$C$6:$C$40,1)),A236&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A236,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A236,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18406,31 +18435,31 @@
       </c>
       <c r="C237" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A237,Sezoane!$C$6:$C$40,1)),A237&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A237,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A237,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D237" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D237" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A237,Sezoane!$C$6:$C$40,1)),A237&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A237,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A237,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E237" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E237" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A237,Sezoane!$C$6:$C$40,1)),A237&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A237,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A237,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F237" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F237" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A237,Sezoane!$C$6:$C$40,1)),A237&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A237,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A237,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G237" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G237" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A237,Sezoane!$C$6:$C$40,1)),A237&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A237,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A237,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H237" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H237" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A237,Sezoane!$C$6:$C$40,1)),A237&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A237,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A237,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I237" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I237" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A237,Sezoane!$C$6:$C$40,1)),A237&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A237,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A237,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18444,31 +18473,31 @@
       </c>
       <c r="C238" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A238,Sezoane!$C$6:$C$40,1)),A238&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A238,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A238,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D238" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D238" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A238,Sezoane!$C$6:$C$40,1)),A238&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A238,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A238,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E238" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E238" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A238,Sezoane!$C$6:$C$40,1)),A238&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A238,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A238,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F238" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F238" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A238,Sezoane!$C$6:$C$40,1)),A238&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A238,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A238,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G238" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G238" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A238,Sezoane!$C$6:$C$40,1)),A238&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A238,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A238,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H238" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H238" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A238,Sezoane!$C$6:$C$40,1)),A238&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A238,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A238,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I238" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I238" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A238,Sezoane!$C$6:$C$40,1)),A238&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A238,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A238,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18482,31 +18511,31 @@
       </c>
       <c r="C239" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A239,Sezoane!$C$6:$C$40,1)),A239&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A239,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A239,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D239" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D239" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A239,Sezoane!$C$6:$C$40,1)),A239&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A239,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A239,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E239" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E239" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A239,Sezoane!$C$6:$C$40,1)),A239&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A239,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A239,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F239" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F239" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A239,Sezoane!$C$6:$C$40,1)),A239&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A239,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A239,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G239" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G239" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A239,Sezoane!$C$6:$C$40,1)),A239&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A239,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A239,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H239" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H239" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A239,Sezoane!$C$6:$C$40,1)),A239&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A239,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A239,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I239" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I239" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A239,Sezoane!$C$6:$C$40,1)),A239&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A239,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A239,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18520,31 +18549,31 @@
       </c>
       <c r="C240" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A240,Sezoane!$C$6:$C$40,1)),A240&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A240,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A240,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D240" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D240" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A240,Sezoane!$C$6:$C$40,1)),A240&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A240,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A240,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E240" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E240" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A240,Sezoane!$C$6:$C$40,1)),A240&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A240,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A240,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F240" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F240" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A240,Sezoane!$C$6:$C$40,1)),A240&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A240,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A240,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G240" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G240" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A240,Sezoane!$C$6:$C$40,1)),A240&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A240,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A240,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H240" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H240" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A240,Sezoane!$C$6:$C$40,1)),A240&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A240,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A240,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I240" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I240" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A240,Sezoane!$C$6:$C$40,1)),A240&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A240,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A240,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18558,31 +18587,31 @@
       </c>
       <c r="C241" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A241,Sezoane!$C$6:$C$40,1)),A241&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A241,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A241,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D241" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D241" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A241,Sezoane!$C$6:$C$40,1)),A241&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A241,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A241,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E241" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E241" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A241,Sezoane!$C$6:$C$40,1)),A241&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A241,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A241,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F241" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F241" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A241,Sezoane!$C$6:$C$40,1)),A241&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A241,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A241,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G241" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G241" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A241,Sezoane!$C$6:$C$40,1)),A241&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A241,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A241,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H241" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H241" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A241,Sezoane!$C$6:$C$40,1)),A241&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A241,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A241,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I241" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I241" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A241,Sezoane!$C$6:$C$40,1)),A241&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A241,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A241,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18596,31 +18625,31 @@
       </c>
       <c r="C242" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A242,Sezoane!$C$6:$C$40,1)),A242&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A242,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A242,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D242" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D242" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A242,Sezoane!$C$6:$C$40,1)),A242&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A242,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A242,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E242" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E242" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A242,Sezoane!$C$6:$C$40,1)),A242&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A242,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A242,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F242" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F242" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A242,Sezoane!$C$6:$C$40,1)),A242&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A242,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A242,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G242" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G242" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A242,Sezoane!$C$6:$C$40,1)),A242&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A242,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A242,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H242" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H242" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A242,Sezoane!$C$6:$C$40,1)),A242&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A242,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A242,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I242" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I242" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A242,Sezoane!$C$6:$C$40,1)),A242&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A242,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A242,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18634,31 +18663,31 @@
       </c>
       <c r="C243" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A243,Sezoane!$C$6:$C$40,1)),A243&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A243,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A243,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D243" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D243" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A243,Sezoane!$C$6:$C$40,1)),A243&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A243,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A243,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E243" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E243" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A243,Sezoane!$C$6:$C$40,1)),A243&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A243,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A243,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F243" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F243" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A243,Sezoane!$C$6:$C$40,1)),A243&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A243,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A243,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G243" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G243" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A243,Sezoane!$C$6:$C$40,1)),A243&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A243,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A243,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H243" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H243" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A243,Sezoane!$C$6:$C$40,1)),A243&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A243,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A243,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I243" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I243" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A243,Sezoane!$C$6:$C$40,1)),A243&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A243,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A243,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18672,31 +18701,31 @@
       </c>
       <c r="C244" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A244,Sezoane!$C$6:$C$40,1)),A244&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A244,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A244,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D244" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D244" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A244,Sezoane!$C$6:$C$40,1)),A244&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A244,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A244,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E244" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E244" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A244,Sezoane!$C$6:$C$40,1)),A244&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A244,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A244,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F244" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F244" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A244,Sezoane!$C$6:$C$40,1)),A244&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A244,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A244,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G244" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G244" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A244,Sezoane!$C$6:$C$40,1)),A244&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A244,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A244,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H244" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H244" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A244,Sezoane!$C$6:$C$40,1)),A244&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A244,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A244,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I244" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I244" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A244,Sezoane!$C$6:$C$40,1)),A244&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A244,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A244,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18710,31 +18739,31 @@
       </c>
       <c r="C245" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A245,Sezoane!$C$6:$C$40,1)),A245&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A245,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A245,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D245" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D245" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A245,Sezoane!$C$6:$C$40,1)),A245&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A245,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A245,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E245" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E245" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A245,Sezoane!$C$6:$C$40,1)),A245&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A245,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A245,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F245" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F245" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A245,Sezoane!$C$6:$C$40,1)),A245&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A245,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A245,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G245" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G245" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A245,Sezoane!$C$6:$C$40,1)),A245&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A245,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A245,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H245" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H245" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A245,Sezoane!$C$6:$C$40,1)),A245&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A245,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A245,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I245" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I245" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A245,Sezoane!$C$6:$C$40,1)),A245&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A245,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A245,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18748,31 +18777,31 @@
       </c>
       <c r="C246" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A246,Sezoane!$C$6:$C$40,1)),A246&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A246,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A246,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D246" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D246" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A246,Sezoane!$C$6:$C$40,1)),A246&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A246,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A246,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E246" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E246" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A246,Sezoane!$C$6:$C$40,1)),A246&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A246,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A246,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F246" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F246" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A246,Sezoane!$C$6:$C$40,1)),A246&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A246,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A246,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G246" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G246" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A246,Sezoane!$C$6:$C$40,1)),A246&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A246,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A246,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H246" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H246" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A246,Sezoane!$C$6:$C$40,1)),A246&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A246,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A246,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I246" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I246" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A246,Sezoane!$C$6:$C$40,1)),A246&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A246,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A246,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18786,31 +18815,31 @@
       </c>
       <c r="C247" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A247,Sezoane!$C$6:$C$40,1)),A247&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A247,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A247,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D247" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D247" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A247,Sezoane!$C$6:$C$40,1)),A247&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A247,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A247,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E247" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E247" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A247,Sezoane!$C$6:$C$40,1)),A247&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A247,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A247,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F247" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F247" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A247,Sezoane!$C$6:$C$40,1)),A247&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A247,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A247,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G247" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G247" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A247,Sezoane!$C$6:$C$40,1)),A247&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A247,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A247,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H247" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H247" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A247,Sezoane!$C$6:$C$40,1)),A247&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A247,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A247,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I247" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I247" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A247,Sezoane!$C$6:$C$40,1)),A247&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A247,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A247,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18824,31 +18853,31 @@
       </c>
       <c r="C248" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A248,Sezoane!$C$6:$C$40,1)),A248&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A248,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A248,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D248" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D248" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A248,Sezoane!$C$6:$C$40,1)),A248&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A248,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A248,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E248" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E248" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A248,Sezoane!$C$6:$C$40,1)),A248&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A248,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A248,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F248" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F248" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A248,Sezoane!$C$6:$C$40,1)),A248&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A248,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A248,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G248" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G248" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A248,Sezoane!$C$6:$C$40,1)),A248&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A248,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A248,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H248" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H248" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A248,Sezoane!$C$6:$C$40,1)),A248&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A248,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A248,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I248" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I248" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A248,Sezoane!$C$6:$C$40,1)),A248&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A248,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A248,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18862,31 +18891,31 @@
       </c>
       <c r="C249" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A249,Sezoane!$C$6:$C$40,1)),A249&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A249,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A249,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D249" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D249" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A249,Sezoane!$C$6:$C$40,1)),A249&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A249,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A249,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E249" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E249" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A249,Sezoane!$C$6:$C$40,1)),A249&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A249,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A249,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F249" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F249" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A249,Sezoane!$C$6:$C$40,1)),A249&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A249,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A249,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G249" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G249" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A249,Sezoane!$C$6:$C$40,1)),A249&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A249,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A249,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H249" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H249" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A249,Sezoane!$C$6:$C$40,1)),A249&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A249,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A249,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I249" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I249" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A249,Sezoane!$C$6:$C$40,1)),A249&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A249,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A249,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18900,31 +18929,31 @@
       </c>
       <c r="C250" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A250,Sezoane!$C$6:$C$40,1)),A250&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A250,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A250,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D250" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D250" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A250,Sezoane!$C$6:$C$40,1)),A250&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A250,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A250,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E250" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E250" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A250,Sezoane!$C$6:$C$40,1)),A250&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A250,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A250,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F250" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F250" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A250,Sezoane!$C$6:$C$40,1)),A250&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A250,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A250,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G250" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G250" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A250,Sezoane!$C$6:$C$40,1)),A250&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A250,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A250,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H250" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H250" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A250,Sezoane!$C$6:$C$40,1)),A250&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A250,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A250,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I250" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I250" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A250,Sezoane!$C$6:$C$40,1)),A250&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A250,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A250,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18938,31 +18967,31 @@
       </c>
       <c r="C251" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A251,Sezoane!$C$6:$C$40,1)),A251&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A251,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A251,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D251" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D251" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A251,Sezoane!$C$6:$C$40,1)),A251&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A251,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A251,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E251" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E251" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A251,Sezoane!$C$6:$C$40,1)),A251&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A251,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A251,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F251" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F251" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A251,Sezoane!$C$6:$C$40,1)),A251&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A251,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A251,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G251" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G251" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A251,Sezoane!$C$6:$C$40,1)),A251&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A251,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A251,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H251" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H251" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A251,Sezoane!$C$6:$C$40,1)),A251&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A251,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A251,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I251" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I251" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A251,Sezoane!$C$6:$C$40,1)),A251&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A251,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A251,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18976,31 +19005,31 @@
       </c>
       <c r="C252" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A252,Sezoane!$C$6:$C$40,1)),A252&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A252,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A252,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D252" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D252" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A252,Sezoane!$C$6:$C$40,1)),A252&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A252,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A252,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E252" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E252" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A252,Sezoane!$C$6:$C$40,1)),A252&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A252,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A252,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F252" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F252" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A252,Sezoane!$C$6:$C$40,1)),A252&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A252,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A252,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G252" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G252" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A252,Sezoane!$C$6:$C$40,1)),A252&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A252,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A252,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H252" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H252" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A252,Sezoane!$C$6:$C$40,1)),A252&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A252,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A252,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I252" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I252" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A252,Sezoane!$C$6:$C$40,1)),A252&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A252,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A252,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19014,31 +19043,31 @@
       </c>
       <c r="C253" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A253,Sezoane!$C$6:$C$40,1)),A253&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A253,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A253,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D253" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D253" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A253,Sezoane!$C$6:$C$40,1)),A253&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A253,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A253,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E253" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E253" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A253,Sezoane!$C$6:$C$40,1)),A253&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A253,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A253,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F253" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F253" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A253,Sezoane!$C$6:$C$40,1)),A253&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A253,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A253,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G253" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G253" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A253,Sezoane!$C$6:$C$40,1)),A253&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A253,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A253,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H253" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H253" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A253,Sezoane!$C$6:$C$40,1)),A253&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A253,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A253,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I253" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I253" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A253,Sezoane!$C$6:$C$40,1)),A253&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A253,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A253,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19052,31 +19081,31 @@
       </c>
       <c r="C254" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A254,Sezoane!$C$6:$C$40,1)),A254&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A254,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A254,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D254" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D254" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A254,Sezoane!$C$6:$C$40,1)),A254&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A254,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A254,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E254" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E254" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A254,Sezoane!$C$6:$C$40,1)),A254&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A254,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A254,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F254" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F254" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A254,Sezoane!$C$6:$C$40,1)),A254&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A254,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A254,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G254" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G254" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A254,Sezoane!$C$6:$C$40,1)),A254&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A254,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A254,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H254" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H254" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A254,Sezoane!$C$6:$C$40,1)),A254&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A254,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A254,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I254" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I254" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A254,Sezoane!$C$6:$C$40,1)),A254&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A254,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A254,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19090,31 +19119,31 @@
       </c>
       <c r="C255" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A255,Sezoane!$C$6:$C$40,1)),A255&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A255,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A255,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D255" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D255" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A255,Sezoane!$C$6:$C$40,1)),A255&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A255,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A255,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E255" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E255" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A255,Sezoane!$C$6:$C$40,1)),A255&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A255,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A255,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F255" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F255" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A255,Sezoane!$C$6:$C$40,1)),A255&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A255,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A255,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G255" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G255" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A255,Sezoane!$C$6:$C$40,1)),A255&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A255,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A255,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H255" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H255" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A255,Sezoane!$C$6:$C$40,1)),A255&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A255,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A255,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I255" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I255" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A255,Sezoane!$C$6:$C$40,1)),A255&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A255,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A255,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19128,31 +19157,31 @@
       </c>
       <c r="C256" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A256,Sezoane!$C$6:$C$40,1)),A256&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A256,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A256,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D256" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D256" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A256,Sezoane!$C$6:$C$40,1)),A256&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A256,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A256,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E256" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E256" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A256,Sezoane!$C$6:$C$40,1)),A256&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A256,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A256,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F256" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F256" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A256,Sezoane!$C$6:$C$40,1)),A256&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A256,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A256,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G256" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G256" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A256,Sezoane!$C$6:$C$40,1)),A256&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A256,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A256,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H256" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H256" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A256,Sezoane!$C$6:$C$40,1)),A256&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A256,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A256,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I256" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I256" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A256,Sezoane!$C$6:$C$40,1)),A256&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A256,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A256,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19166,31 +19195,31 @@
       </c>
       <c r="C257" s="42" t="str">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A257,Sezoane!$C$6:$C$40,1)),A257&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A257,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$A$6:$A$40,MATCH(A257,Sezoane!$C$6:$C$40,1)),"⚠ fără sezon")</f>
-        <v>⚠ fără sezon</v>
-      </c>
-      <c r="D257" s="42" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="D257" s="43" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A257,Sezoane!$C$6:$C$40,1)),A257&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A257,Sezoane!$C$6:$C$40,1))),INDEX(Sezoane!$F$6:$F$40,MATCH(A257,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="E257" s="44" t="str">
+        <v>2</v>
+      </c>
+      <c r="E257" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A257,Sezoane!$C$6:$C$40,1)),A257&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A257,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$E$5:$E$39,MATCH(A257,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="F257" s="44" t="str">
+        <v>900</v>
+      </c>
+      <c r="F257" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A257,Sezoane!$C$6:$C$40,1)),A257&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A257,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$F$5:$F$39,MATCH(A257,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="G257" s="44" t="str">
+        <v>1130</v>
+      </c>
+      <c r="G257" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A257,Sezoane!$C$6:$C$40,1)),A257&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A257,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$G$5:$G$39,MATCH(A257,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="H257" s="44" t="str">
+        <v>1020</v>
+      </c>
+      <c r="H257" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A257,Sezoane!$C$6:$C$40,1)),A257&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A257,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$H$5:$H$39,MATCH(A257,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
-      </c>
-      <c r="I257" s="44" t="str">
+        <v>980</v>
+      </c>
+      <c r="I257" s="44" t="n">
         <f aca="false">IF(AND(ISNUMBER(MATCH(A257,Sezoane!$C$6:$C$40,1)),A257&lt;=INDEX(Sezoane!$D$6:$D$40,MATCH(A257,Sezoane!$C$6:$C$40,1))),INDEX('Prețuri de setat'!$I$5:$I$39,MATCH(A257,Sezoane!$C$6:$C$40,1)),"")</f>
-        <v/>
+        <v>852</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23485,7 +23514,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23494,7 +23523,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -23510,257 +23539,257 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C6" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D9" s="45" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C10" s="45" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="45" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D13" s="45" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D14" s="45" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D15" s="45" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D16" s="45" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="45" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D18" s="45" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -23804,7 +23833,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23831,26 +23860,26 @@
         <v>45</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23885,7 +23914,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="47" t="n">
         <f aca="false">MAX(Sezoane!D6:D40)</f>
-        <v>46453</v>
+        <v>46568</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24036,9 +24065,9 @@
         <f aca="false">IF(Sezoane!$A$11="","",IF(Sezoane!D11&lt;Sezoane!C11,"⚠ sfârșit înainte de început",IF(OR(Sezoane!A12="",12&gt;40),"OK",IF(Sezoane!C12&lt;=Sezoane!D11,"⚠ se suprapune / neordonat","OK"))))</f>
         <v>OK</v>
       </c>
-      <c r="E9" s="46" t="str">
+      <c r="E9" s="46" t="n">
         <f aca="false">IF(Sezoane!$A$11="","",IF(Sezoane!A12="","ultimul sezon",Sezoane!C12-Sezoane!D11-1))</f>
-        <v>ultimul sezon</v>
+        <v>0</v>
       </c>
       <c r="F9" s="46" t="str">
         <f aca="false">IF(Sezoane!$A$11="","",IF(ISNUMBER(INDEX(Sezoane!G11:L11,1,MAX(1,Sezoane!F11-1))),"OK",IF(COUNT(Sezoane!G11:L11)=0,"OK (fără reduceri)","⚠ pune 0% la durata minimă")))</f>
@@ -24054,31 +24083,31 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!A12)</f>
-        <v/>
-      </c>
-      <c r="B10" s="39" t="str">
+        <v>primavara-2027</v>
+      </c>
+      <c r="B10" s="39" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!C12)</f>
-        <v/>
-      </c>
-      <c r="C10" s="39" t="str">
+        <v>46454</v>
+      </c>
+      <c r="C10" s="39" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!D12)</f>
-        <v/>
+        <v>46568</v>
       </c>
       <c r="D10" s="46" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",IF(Sezoane!D12&lt;Sezoane!C12,"⚠ sfârșit înainte de început",IF(OR(Sezoane!A13="",13&gt;40),"OK",IF(Sezoane!C13&lt;=Sezoane!D12,"⚠ se suprapune / neordonat","OK"))))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="E10" s="46" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",IF(Sezoane!A13="","ultimul sezon",Sezoane!C13-Sezoane!D12-1))</f>
-        <v/>
+        <v>ultimul sezon</v>
       </c>
       <c r="F10" s="46" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",IF(ISNUMBER(INDEX(Sezoane!G12:L12,1,MAX(1,Sezoane!F12-1))),"OK",IF(COUNT(Sezoane!G12:L12)=0,"OK (fără reduceri)","⚠ pune 0% la durata minimă")))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="G10" s="46" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",IF(AND(D10="OK",OR(E10="ultimul sezon",E10=0)),"OK","⚠ verifică"))</f>
-        <v/>
+        <v>OK</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -25012,7 +25041,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -25022,7 +25051,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -25051,19 +25080,19 @@
         <v>45</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25071,7 +25100,7 @@
         <v>60</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C6" s="48" t="n">
         <v>1130</v>
@@ -25083,7 +25112,7 @@
         <v>980</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25091,7 +25120,7 @@
         <v>63</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C7" s="48" t="n">
         <v>1580</v>
@@ -25103,7 +25132,7 @@
         <v>1360</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25111,7 +25140,7 @@
         <v>65</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C8" s="48" t="n">
         <v>1890</v>
@@ -25123,7 +25152,7 @@
         <v>1630</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25131,7 +25160,7 @@
         <v>68</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C9" s="48" t="n">
         <v>2270</v>
@@ -25143,7 +25172,7 @@
         <v>1960</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25151,7 +25180,7 @@
         <v>69</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C10" s="48" t="n">
         <v>1700</v>
@@ -25163,7 +25192,7 @@
         <v>1470</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25171,7 +25200,7 @@
         <v>70</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C11" s="48" t="n">
         <v>1830</v>
@@ -25183,15 +25212,15 @@
         <v>1580</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>241</v>
+        <v>71</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C12" s="48" t="n">
         <v>900</v>
@@ -25203,7 +25232,7 @@
         <v>1380</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25224,7 +25253,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -25234,7 +25263,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
@@ -25244,7 +25273,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B17" s="49"/>
       <c r="C17" s="49"/>
@@ -25254,7 +25283,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
@@ -25264,7 +25293,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B19" s="49"/>
       <c r="C19" s="49"/>
@@ -25274,7 +25303,7 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -25284,7 +25313,7 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B21" s="49"/>
       <c r="C21" s="49"/>

--- a/pricing/tarife.xlsx
+++ b/pricing/tarife.xlsx
@@ -883,7 +883,7 @@
     <t xml:space="preserve">08.03 – 30.06.2027</t>
   </si>
   <si>
-    <t xml:space="preserve">Înainte de setare (21.10.2026): site blocat (fără sezon), Booking/Airbnb 900, Travelminit 1.380, Travelminit fără reguli din 08.03.</t>
+    <t xml:space="preserve">Setat 21.10.2026 (înainte: site blocat, Booking/Airbnb 900, Travelminit 1.380 fără reguli). Iunie deschis pe Booking (era închis din 01.06 și bloca prin iCal Airbnb/Travelminit/site). Travelminit: min 2, politică standard. Site 900.</t>
   </si>
   <si>
     <t xml:space="preserve">Comisioane și setări observate</t>
@@ -5714,15 +5714,15 @@
       </c>
       <c r="L11" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IFERROR(INDEX('Date actuale'!$C$6:$C$40,MATCH(A11,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>900</v>
+        <v>1130</v>
       </c>
       <c r="M11" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IFERROR(INDEX('Date actuale'!$D$6:$D$40,MATCH(A11,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>900</v>
+        <v>1020</v>
       </c>
       <c r="N11" s="32" t="n">
         <f aca="false">IF(Sezoane!$A$12="","",IFERROR(INDEX('Date actuale'!$E$6:$E$40,MATCH(A11,'Date actuale'!$A$6:$A$40,0)),""))</f>
-        <v>1380</v>
+        <v>980</v>
       </c>
       <c r="O11" s="25" t="str">
         <f aca="false">IF(Sezoane!$A$12="","",Sezoane!M12)</f>
@@ -25223,13 +25223,13 @@
         <v>243</v>
       </c>
       <c r="C12" s="48" t="n">
-        <v>900</v>
+        <v>1130</v>
       </c>
       <c r="D12" s="48" t="n">
-        <v>900</v>
+        <v>1020</v>
       </c>
       <c r="E12" s="48" t="n">
-        <v>1380</v>
+        <v>980</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>244</v>

--- a/pricing/tarife.xlsx
+++ b/pricing/tarife.xlsx
@@ -399,7 +399,7 @@
     <t xml:space="preserve">Comision platformă</t>
   </si>
   <si>
-    <t xml:space="preserve">Booking 15% (din rezervările 6131205469, 5429915812, 6470558532). Airbnb: taxă unică gazdă 15,5% (editor Airbnb: 1.480 lei → câștigi 1.251 lei). Travelminit: „Nivelul de comisionare actual 12%” (admin → Îmbunătățirea poziției).</t>
+    <t xml:space="preserve">Booking 15% (din 3 rezervări Booking reale). Airbnb: taxă unică gazdă 15,5% (editor Airbnb: 1.480 lei → câștigi 1.251 lei). Travelminit: „Nivelul de comisionare actual 12%” (admin → Îmbunătățirea poziției).</t>
   </si>
   <si>
     <t xml:space="preserve">Costuri procesare plată</t>
@@ -889,10 +889,10 @@
     <t xml:space="preserve">Comisioane și setări observate</t>
   </si>
   <si>
-    <t xml:space="preserve">Booking: rez. 6131205469 – suma comisionabilă 3.633 lei, comision și costuri 596,55 lei (16,4%); total oaspete 3.969 lei (taxe locale 336 lei incluse, scăzute din baza de comision).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Booking: rez. 5429915812 – 1.362 lei comisionabil, 223,25 lei comision (16,4%); rez. 6470558532 – 2.253 lei, 368,49 lei (16,4%).</t>
+    <t xml:space="preserve">Booking, rezervarea 1 – suma comisionabilă 3.633 lei, comision și costuri 596,55 lei (16,4%); total oaspete 3.969 lei (taxe locale 336 lei incluse, scăzute din baza de comision).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booking, rezervarea 2 – 1.362 lei comisionabil, 223,25 lei comision (16,4%); rezervarea 3 – 2.253 lei, 368,49 lei (16,4%).</t>
   </si>
   <si>
     <t xml:space="preserve">Booking: Standard Rate nerambursabil; planuri derivate 2–7 zile (-10% … -33%), flexibile 14 zile; plan „Sarbatori – Nerambursabil”; Mobile rate 10% activ din 07.06.2026; Genius neactiv.</t>
